--- a/research/traditional_assets/database/data/estonia/estonia_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_real_estate_general_diversified.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07358156419369684</v>
+        <v>0.07347040106530943</v>
       </c>
       <c r="C2">
-        <v>33.06736540186152</v>
+        <v>32.76726216037947</v>
       </c>
       <c r="D2">
-        <v>31.77736540186152</v>
+        <v>31.80726216037947</v>
       </c>
       <c r="E2">
-        <v>-17.6</v>
+        <v>-17.27</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="G2">
         <v>1.29</v>
@@ -1445,28 +1445,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.016599</v>
       </c>
       <c r="N2">
-        <v>5.022244897959184</v>
+        <v>5.005645897959184</v>
       </c>
       <c r="O2">
-        <v>1.004448979591837</v>
+        <v>1.001129179591837</v>
       </c>
       <c r="P2">
-        <v>4.017795918367347</v>
+        <v>4.004516718367347</v>
       </c>
       <c r="Q2">
-        <v>4.107795918367347</v>
+        <v>4.094516718367347</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07358156419369684</v>
+        <v>0.07380606168213075</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313375</v>
+        <v>0.5312646412299745</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>302.5631000638101</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07347040106530943</v>
+        <v>0.07335923793692203</v>
       </c>
       <c r="C3">
-        <v>32.76726216037947</v>
+        <v>32.46721522676749</v>
       </c>
       <c r="D3">
-        <v>31.80726216037947</v>
+        <v>31.83721522676749</v>
       </c>
       <c r="E3">
-        <v>-17.27</v>
+        <v>-16.94</v>
       </c>
       <c r="F3">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="G3">
         <v>1.29</v>
@@ -1527,28 +1527,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M3">
-        <v>0.016599</v>
+        <v>0.033198</v>
       </c>
       <c r="N3">
-        <v>5.005645897959184</v>
+        <v>4.989046897959184</v>
       </c>
       <c r="O3">
-        <v>1.001129179591837</v>
+        <v>0.9978093795918369</v>
       </c>
       <c r="P3">
-        <v>4.004516718367347</v>
+        <v>3.991237518367348</v>
       </c>
       <c r="Q3">
-        <v>4.094516718367347</v>
+        <v>4.081237518367347</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07380606168213075</v>
+        <v>0.07403514075196127</v>
       </c>
       <c r="T3">
-        <v>0.5312646412299745</v>
+        <v>0.5356101865347063</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>302.5631000638101</v>
+        <v>151.2815500319051</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07335923793692203</v>
+        <v>0.07324807480853467</v>
       </c>
       <c r="C4">
-        <v>32.46721522676749</v>
+        <v>32.16722476025178</v>
       </c>
       <c r="D4">
-        <v>31.83721522676749</v>
+        <v>31.86722476025178</v>
       </c>
       <c r="E4">
-        <v>-16.94</v>
+        <v>-16.61</v>
       </c>
       <c r="F4">
-        <v>0.66</v>
+        <v>0.99</v>
       </c>
       <c r="G4">
         <v>1.29</v>
@@ -1609,28 +1609,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M4">
-        <v>0.033198</v>
+        <v>0.04979699999999999</v>
       </c>
       <c r="N4">
-        <v>4.989046897959184</v>
+        <v>4.972447897959184</v>
       </c>
       <c r="O4">
-        <v>0.9978093795918369</v>
+        <v>0.9944895795918369</v>
       </c>
       <c r="P4">
-        <v>3.991237518367348</v>
+        <v>3.977958318367347</v>
       </c>
       <c r="Q4">
-        <v>4.081237518367347</v>
+        <v>4.067958318367348</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07403514075196127</v>
+        <v>0.07426894310158212</v>
       </c>
       <c r="T4">
-        <v>0.5356101865347063</v>
+        <v>0.5400453307117005</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>151.2815500319051</v>
+        <v>100.8543666879367</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07324807480853467</v>
+        <v>0.07313691168014727</v>
       </c>
       <c r="C5">
-        <v>32.16722476025178</v>
+        <v>31.86729092065946</v>
       </c>
       <c r="D5">
-        <v>31.86722476025178</v>
+        <v>31.89729092065947</v>
       </c>
       <c r="E5">
-        <v>-16.61</v>
+        <v>-16.28</v>
       </c>
       <c r="F5">
-        <v>0.99</v>
+        <v>1.32</v>
       </c>
       <c r="G5">
         <v>1.29</v>
@@ -1691,28 +1691,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M5">
-        <v>0.04979699999999999</v>
+        <v>0.066396</v>
       </c>
       <c r="N5">
-        <v>4.972447897959184</v>
+        <v>4.955848897959184</v>
       </c>
       <c r="O5">
-        <v>0.9944895795918369</v>
+        <v>0.9911697795918368</v>
       </c>
       <c r="P5">
-        <v>3.977958318367347</v>
+        <v>3.964679118367347</v>
       </c>
       <c r="Q5">
-        <v>4.067958318367348</v>
+        <v>4.054679118367347</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07426894310158212</v>
+        <v>0.07450761633348674</v>
       </c>
       <c r="T5">
-        <v>0.5400453307117005</v>
+        <v>0.5445728737257154</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>100.8543666879367</v>
+        <v>75.64077501595253</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07313691168014727</v>
+        <v>0.07302574855175986</v>
       </c>
       <c r="C6">
-        <v>31.86729092065946</v>
+        <v>31.5674138684214</v>
       </c>
       <c r="D6">
-        <v>31.89729092065947</v>
+        <v>31.92741386842139</v>
       </c>
       <c r="E6">
-        <v>-16.28</v>
+        <v>-15.95</v>
       </c>
       <c r="F6">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="G6">
         <v>1.29</v>
@@ -1773,28 +1773,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M6">
-        <v>0.066396</v>
+        <v>0.082995</v>
       </c>
       <c r="N6">
-        <v>4.955848897959184</v>
+        <v>4.939249897959184</v>
       </c>
       <c r="O6">
-        <v>0.9911697795918368</v>
+        <v>0.9878499795918367</v>
       </c>
       <c r="P6">
-        <v>3.964679118367347</v>
+        <v>3.951399918367347</v>
       </c>
       <c r="Q6">
-        <v>4.054679118367347</v>
+        <v>4.041399918367347</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07450761633348674</v>
+        <v>0.07475131426501039</v>
       </c>
       <c r="T6">
-        <v>0.5445728737257154</v>
+        <v>0.5491957334347621</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>75.64077501595253</v>
+        <v>60.51262001276202</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07302574855175986</v>
+        <v>0.07291458542337247</v>
       </c>
       <c r="C7">
-        <v>31.5674138684214</v>
+        <v>31.26759376457501</v>
       </c>
       <c r="D7">
-        <v>31.92741386842139</v>
+        <v>31.95759376457501</v>
       </c>
       <c r="E7">
-        <v>-15.95</v>
+        <v>-15.62</v>
       </c>
       <c r="F7">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="G7">
         <v>1.29</v>
@@ -1855,28 +1855,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M7">
-        <v>0.082995</v>
+        <v>0.099594</v>
       </c>
       <c r="N7">
-        <v>4.939249897959184</v>
+        <v>4.922650897959184</v>
       </c>
       <c r="O7">
-        <v>0.9878499795918367</v>
+        <v>0.9845301795918369</v>
       </c>
       <c r="P7">
-        <v>3.951399918367347</v>
+        <v>3.938120718367347</v>
       </c>
       <c r="Q7">
-        <v>4.041399918367347</v>
+        <v>4.028120718367347</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07475131426501039</v>
+        <v>0.07500019725890689</v>
       </c>
       <c r="T7">
-        <v>0.5491957334347621</v>
+        <v>0.5539169518610229</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>60.51262001276202</v>
+        <v>50.42718334396835</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07291458542337247</v>
+        <v>0.07280342229498507</v>
       </c>
       <c r="C8">
-        <v>31.26759376457501</v>
+        <v>30.96783077076723</v>
       </c>
       <c r="D8">
-        <v>31.95759376457501</v>
+        <v>31.98783077076722</v>
       </c>
       <c r="E8">
-        <v>-15.62</v>
+        <v>-15.29</v>
       </c>
       <c r="F8">
-        <v>1.98</v>
+        <v>2.31</v>
       </c>
       <c r="G8">
         <v>1.29</v>
@@ -1937,28 +1937,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M8">
-        <v>0.09959399999999999</v>
+        <v>0.116193</v>
       </c>
       <c r="N8">
-        <v>4.922650897959184</v>
+        <v>4.906051897959184</v>
       </c>
       <c r="O8">
-        <v>0.9845301795918369</v>
+        <v>0.9812103795918369</v>
       </c>
       <c r="P8">
-        <v>3.938120718367347</v>
+        <v>3.924841518367347</v>
       </c>
       <c r="Q8">
-        <v>4.028120718367347</v>
+        <v>4.014841518367347</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07500019725890689</v>
+        <v>0.07525443257525277</v>
       </c>
       <c r="T8">
-        <v>0.5539169518610229</v>
+        <v>0.5587397018663428</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>50.42718334396836</v>
+        <v>43.22330000911574</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07280342229498507</v>
+        <v>0.07269225916659769</v>
       </c>
       <c r="C9">
-        <v>30.96783077076723</v>
+        <v>30.66812504925733</v>
       </c>
       <c r="D9">
-        <v>31.98783077076722</v>
+        <v>32.01812504925733</v>
       </c>
       <c r="E9">
-        <v>-15.29</v>
+        <v>-14.96</v>
       </c>
       <c r="F9">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="G9">
         <v>1.29</v>
@@ -2019,28 +2019,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M9">
-        <v>0.116193</v>
+        <v>0.132792</v>
       </c>
       <c r="N9">
-        <v>4.906051897959184</v>
+        <v>4.889452897959184</v>
       </c>
       <c r="O9">
-        <v>0.9812103795918369</v>
+        <v>0.9778905795918368</v>
       </c>
       <c r="P9">
-        <v>3.924841518367347</v>
+        <v>3.911562318367347</v>
       </c>
       <c r="Q9">
-        <v>4.014841518367347</v>
+        <v>4.001562318367347</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07525443257525277</v>
+        <v>0.07551419474630183</v>
       </c>
       <c r="T9">
-        <v>0.5587397018663428</v>
+        <v>0.5636672942630827</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>43.22330000911573</v>
+        <v>37.82038750797626</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07269225916659769</v>
+        <v>0.07258109603821029</v>
       </c>
       <c r="C10">
-        <v>30.66812504925733</v>
+        <v>30.36847676291985</v>
       </c>
       <c r="D10">
-        <v>32.01812504925733</v>
+        <v>32.04847676291985</v>
       </c>
       <c r="E10">
-        <v>-14.96</v>
+        <v>-14.63</v>
       </c>
       <c r="F10">
-        <v>2.64</v>
+        <v>2.97</v>
       </c>
       <c r="G10">
         <v>1.29</v>
@@ -2101,28 +2101,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M10">
-        <v>0.132792</v>
+        <v>0.149391</v>
       </c>
       <c r="N10">
-        <v>4.889452897959184</v>
+        <v>4.872853897959184</v>
       </c>
       <c r="O10">
-        <v>0.9778905795918368</v>
+        <v>0.9745707795918369</v>
       </c>
       <c r="P10">
-        <v>3.911562318367347</v>
+        <v>3.898283118367348</v>
       </c>
       <c r="Q10">
-        <v>4.001562318367347</v>
+        <v>3.988283118367348</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07551419474630183</v>
+        <v>0.07577966597605526</v>
       </c>
       <c r="T10">
-        <v>0.5636672942630827</v>
+        <v>0.5687031853938169</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>37.82038750797626</v>
+        <v>33.61812222931224</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07258109603821029</v>
+        <v>0.0724699329098229</v>
       </c>
       <c r="C11">
-        <v>30.36847676291985</v>
+        <v>30.06888607524749</v>
       </c>
       <c r="D11">
-        <v>32.04847676291985</v>
+        <v>32.0788860752475</v>
       </c>
       <c r="E11">
-        <v>-14.63</v>
+        <v>-14.3</v>
       </c>
       <c r="F11">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="G11">
         <v>1.29</v>
@@ -2183,28 +2183,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M11">
-        <v>0.149391</v>
+        <v>0.16599</v>
       </c>
       <c r="N11">
-        <v>4.872853897959184</v>
+        <v>4.856254897959184</v>
       </c>
       <c r="O11">
-        <v>0.9745707795918369</v>
+        <v>0.9712509795918369</v>
       </c>
       <c r="P11">
-        <v>3.898283118367348</v>
+        <v>3.885003918367347</v>
       </c>
       <c r="Q11">
-        <v>3.988283118367348</v>
+        <v>3.975003918367347</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07577966597605526</v>
+        <v>0.07605103656646989</v>
       </c>
       <c r="T11">
-        <v>0.5687031853938169</v>
+        <v>0.5738509852163451</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>33.61812222931224</v>
+        <v>30.25631000638102</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0724699329098229</v>
+        <v>0.07235876978143549</v>
       </c>
       <c r="C12">
-        <v>30.06888607524749</v>
+        <v>29.7693531503541</v>
       </c>
       <c r="D12">
-        <v>32.0788860752475</v>
+        <v>32.1093531503541</v>
       </c>
       <c r="E12">
-        <v>-14.3</v>
+        <v>-13.97</v>
       </c>
       <c r="F12">
-        <v>3.3</v>
+        <v>3.63</v>
       </c>
       <c r="G12">
         <v>1.29</v>
@@ -2265,28 +2265,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M12">
-        <v>0.16599</v>
+        <v>0.182589</v>
       </c>
       <c r="N12">
-        <v>4.856254897959184</v>
+        <v>4.839655897959184</v>
       </c>
       <c r="O12">
-        <v>0.9712509795918369</v>
+        <v>0.9679311795918368</v>
       </c>
       <c r="P12">
-        <v>3.885003918367347</v>
+        <v>3.871724718367347</v>
       </c>
       <c r="Q12">
-        <v>3.975003918367347</v>
+        <v>3.961724718367347</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07605103656646989</v>
+        <v>0.07632850537239944</v>
       </c>
       <c r="T12">
-        <v>0.5738509852163454</v>
+        <v>0.5791144659337618</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>30.25631000638101</v>
+        <v>27.50573636943729</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07235876978143549</v>
+        <v>0.07224760665304811</v>
       </c>
       <c r="C13">
-        <v>29.7693531503541</v>
+        <v>29.46987815297752</v>
       </c>
       <c r="D13">
-        <v>32.1093531503541</v>
+        <v>32.13987815297752</v>
       </c>
       <c r="E13">
-        <v>-13.97</v>
+        <v>-13.64</v>
       </c>
       <c r="F13">
-        <v>3.63</v>
+        <v>3.96</v>
       </c>
       <c r="G13">
         <v>1.29</v>
@@ -2347,28 +2347,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M13">
-        <v>0.182589</v>
+        <v>0.199188</v>
       </c>
       <c r="N13">
-        <v>4.839655897959184</v>
+        <v>4.823056897959184</v>
       </c>
       <c r="O13">
-        <v>0.9679311795918368</v>
+        <v>0.9646113795918367</v>
       </c>
       <c r="P13">
-        <v>3.871724718367347</v>
+        <v>3.858445518367347</v>
       </c>
       <c r="Q13">
-        <v>3.961724718367347</v>
+        <v>3.948445518367347</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07632850537239944</v>
+        <v>0.07661228028755468</v>
       </c>
       <c r="T13">
-        <v>0.5791144659337618</v>
+        <v>0.584497571212938</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>27.50573636943729</v>
+        <v>25.21359167198418</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07224760665304811</v>
+        <v>0.07213644352466073</v>
       </c>
       <c r="C14">
-        <v>29.46987815297752</v>
+        <v>29.1704612484827</v>
       </c>
       <c r="D14">
-        <v>32.13987815297752</v>
+        <v>32.1704612484827</v>
       </c>
       <c r="E14">
-        <v>-13.64</v>
+        <v>-13.31</v>
       </c>
       <c r="F14">
-        <v>3.96</v>
+        <v>4.29</v>
       </c>
       <c r="G14">
         <v>1.29</v>
@@ -2429,28 +2429,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M14">
-        <v>0.199188</v>
+        <v>0.215787</v>
       </c>
       <c r="N14">
-        <v>4.823056897959184</v>
+        <v>4.806457897959184</v>
       </c>
       <c r="O14">
-        <v>0.9646113795918367</v>
+        <v>0.9612915795918369</v>
       </c>
       <c r="P14">
-        <v>3.858445518367347</v>
+        <v>3.845166318367347</v>
       </c>
       <c r="Q14">
-        <v>3.948445518367347</v>
+        <v>3.935166318367347</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07661228028755468</v>
+        <v>0.07690257876397784</v>
       </c>
       <c r="T14">
-        <v>0.584497571212938</v>
+        <v>0.5900044260387617</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.21359167198418</v>
+        <v>23.27408462029309</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07213644352466073</v>
+        <v>0.07202528039627332</v>
       </c>
       <c r="C15">
-        <v>29.1704612484827</v>
+        <v>28.87110260286457</v>
       </c>
       <c r="D15">
-        <v>32.1704612484827</v>
+        <v>32.20110260286457</v>
       </c>
       <c r="E15">
-        <v>-13.31</v>
+        <v>-12.98</v>
       </c>
       <c r="F15">
-        <v>4.29</v>
+        <v>4.62</v>
       </c>
       <c r="G15">
         <v>1.29</v>
@@ -2511,28 +2511,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M15">
-        <v>0.215787</v>
+        <v>0.232386</v>
       </c>
       <c r="N15">
-        <v>4.806457897959184</v>
+        <v>4.789858897959184</v>
       </c>
       <c r="O15">
-        <v>0.9612915795918369</v>
+        <v>0.9579717795918369</v>
       </c>
       <c r="P15">
-        <v>3.845166318367347</v>
+        <v>3.831887118367347</v>
       </c>
       <c r="Q15">
-        <v>3.935166318367347</v>
+        <v>3.921887118367347</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07690257876397784</v>
+        <v>0.07719962836775968</v>
       </c>
       <c r="T15">
-        <v>0.5900044260387617</v>
+        <v>0.5956393472558837</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.27408462029309</v>
+        <v>21.61165000455787</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07202528039627332</v>
+        <v>0.07191411726788594</v>
       </c>
       <c r="C16">
-        <v>28.87110260286457</v>
+        <v>28.57180238275109</v>
       </c>
       <c r="D16">
-        <v>32.20110260286457</v>
+        <v>32.23180238275109</v>
       </c>
       <c r="E16">
-        <v>-12.98</v>
+        <v>-12.65</v>
       </c>
       <c r="F16">
-        <v>4.62</v>
+        <v>4.950000000000001</v>
       </c>
       <c r="G16">
         <v>1.29</v>
@@ -2593,28 +2593,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M16">
-        <v>0.232386</v>
+        <v>0.248985</v>
       </c>
       <c r="N16">
-        <v>4.789858897959184</v>
+        <v>4.773259897959184</v>
       </c>
       <c r="O16">
-        <v>0.9579717795918369</v>
+        <v>0.9546519795918368</v>
       </c>
       <c r="P16">
-        <v>3.831887118367347</v>
+        <v>3.818607918367347</v>
       </c>
       <c r="Q16">
-        <v>3.921887118367347</v>
+        <v>3.908607918367347</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07719962836775968</v>
+        <v>0.07750366737398345</v>
       </c>
       <c r="T16">
-        <v>0.5956393472558837</v>
+        <v>0.6014068548545851</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.61165000455787</v>
+        <v>20.17087333758734</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07191411726788594</v>
+        <v>0.07180295413949853</v>
       </c>
       <c r="C17">
-        <v>28.57180238275109</v>
+        <v>28.27256075540628</v>
       </c>
       <c r="D17">
-        <v>32.23180238275109</v>
+        <v>32.26256075540628</v>
       </c>
       <c r="E17">
-        <v>-12.65</v>
+        <v>-12.32</v>
       </c>
       <c r="F17">
-        <v>4.95</v>
+        <v>5.28</v>
       </c>
       <c r="G17">
         <v>1.29</v>
@@ -2675,28 +2675,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M17">
-        <v>0.248985</v>
+        <v>0.265584</v>
       </c>
       <c r="N17">
-        <v>4.773259897959184</v>
+        <v>4.756660897959184</v>
       </c>
       <c r="O17">
-        <v>0.9546519795918368</v>
+        <v>0.9513321795918369</v>
       </c>
       <c r="P17">
-        <v>3.818607918367347</v>
+        <v>3.805328718367348</v>
       </c>
       <c r="Q17">
-        <v>3.908607918367347</v>
+        <v>3.895328718367348</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07750366737398345</v>
+        <v>0.07781494540416492</v>
       </c>
       <c r="T17">
-        <v>0.6014068548545851</v>
+        <v>0.6073116840627794</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.17087333758734</v>
+        <v>18.91019375398814</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07180295413949853</v>
+        <v>0.07169179101111113</v>
       </c>
       <c r="C18">
-        <v>28.27256075540628</v>
+        <v>27.9733778887332</v>
       </c>
       <c r="D18">
-        <v>32.26256075540628</v>
+        <v>32.2933778887332</v>
       </c>
       <c r="E18">
-        <v>-12.32</v>
+        <v>-11.99</v>
       </c>
       <c r="F18">
-        <v>5.28</v>
+        <v>5.61</v>
       </c>
       <c r="G18">
         <v>1.29</v>
@@ -2757,28 +2757,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M18">
-        <v>0.265584</v>
+        <v>0.282183</v>
       </c>
       <c r="N18">
-        <v>4.756660897959184</v>
+        <v>4.740061897959184</v>
       </c>
       <c r="O18">
-        <v>0.9513321795918369</v>
+        <v>0.9480123795918369</v>
       </c>
       <c r="P18">
-        <v>3.805328718367348</v>
+        <v>3.792049518367347</v>
       </c>
       <c r="Q18">
-        <v>3.895328718367348</v>
+        <v>3.882049518367347</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07781494540416492</v>
+        <v>0.07813372410977246</v>
       </c>
       <c r="T18">
-        <v>0.6073116840627794</v>
+        <v>0.6133587983121349</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.91019375398814</v>
+        <v>17.79782941551824</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07169179101111113</v>
+        <v>0.07158062788272376</v>
       </c>
       <c r="C19">
-        <v>27.9733778887332</v>
+        <v>27.67425395127707</v>
       </c>
       <c r="D19">
-        <v>32.2933778887332</v>
+        <v>32.32425395127707</v>
       </c>
       <c r="E19">
-        <v>-11.99</v>
+        <v>-11.66</v>
       </c>
       <c r="F19">
-        <v>5.61</v>
+        <v>5.94</v>
       </c>
       <c r="G19">
         <v>1.29</v>
@@ -2839,28 +2839,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M19">
-        <v>0.282183</v>
+        <v>0.298782</v>
       </c>
       <c r="N19">
-        <v>4.740061897959184</v>
+        <v>4.723462897959184</v>
       </c>
       <c r="O19">
-        <v>0.9480123795918369</v>
+        <v>0.9446925795918368</v>
       </c>
       <c r="P19">
-        <v>3.792049518367347</v>
+        <v>3.778770318367347</v>
       </c>
       <c r="Q19">
-        <v>3.882049518367347</v>
+        <v>3.868770318367347</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07813372410977246</v>
+        <v>0.07846027790576068</v>
       </c>
       <c r="T19">
-        <v>0.6133587983121349</v>
+        <v>0.6195534031529383</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.79782941551824</v>
+        <v>16.80906111465612</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07158062788272376</v>
+        <v>0.07146946475433637</v>
       </c>
       <c r="C20">
-        <v>27.67425395127707</v>
+        <v>27.37518911222835</v>
       </c>
       <c r="D20">
-        <v>32.32425395127707</v>
+        <v>32.35518911222835</v>
       </c>
       <c r="E20">
-        <v>-11.66</v>
+        <v>-11.33</v>
       </c>
       <c r="F20">
-        <v>5.94</v>
+        <v>6.27</v>
       </c>
       <c r="G20">
         <v>1.29</v>
@@ -2921,28 +2921,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M20">
-        <v>0.2987819999999999</v>
+        <v>0.315381</v>
       </c>
       <c r="N20">
-        <v>4.723462897959184</v>
+        <v>4.706863897959184</v>
       </c>
       <c r="O20">
-        <v>0.9446925795918368</v>
+        <v>0.9413727795918367</v>
       </c>
       <c r="P20">
-        <v>3.778770318367347</v>
+        <v>3.765491118367347</v>
       </c>
       <c r="Q20">
-        <v>3.868770318367347</v>
+        <v>3.855491118367347</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07846027790576067</v>
+        <v>0.07879489475843995</v>
       </c>
       <c r="T20">
-        <v>0.6195534031529382</v>
+        <v>0.6259009611996873</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.80906111465612</v>
+        <v>15.92437368756895</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07146946475433637</v>
+        <v>0.07135830162594896</v>
       </c>
       <c r="C21">
-        <v>27.37518911222835</v>
+        <v>27.07618354142574</v>
       </c>
       <c r="D21">
-        <v>32.35518911222835</v>
+        <v>32.38618354142574</v>
       </c>
       <c r="E21">
-        <v>-11.33</v>
+        <v>-11</v>
       </c>
       <c r="F21">
-        <v>6.27</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="G21">
         <v>1.29</v>
@@ -3003,28 +3003,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M21">
-        <v>0.315381</v>
+        <v>0.33198</v>
       </c>
       <c r="N21">
-        <v>4.706863897959184</v>
+        <v>4.690264897959184</v>
       </c>
       <c r="O21">
-        <v>0.9413727795918367</v>
+        <v>0.9380529795918369</v>
       </c>
       <c r="P21">
-        <v>3.765491118367347</v>
+        <v>3.752211918367347</v>
       </c>
       <c r="Q21">
-        <v>3.855491118367347</v>
+        <v>3.842211918367347</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07879489475843995</v>
+        <v>0.0791378770324362</v>
       </c>
       <c r="T21">
-        <v>0.6259009611996873</v>
+        <v>0.632407208197605</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.92437368756895</v>
+        <v>15.12815500319051</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07135830162594896</v>
+        <v>0.07124713849756156</v>
       </c>
       <c r="C22">
-        <v>27.07618354142574</v>
+        <v>26.7772374093594</v>
       </c>
       <c r="D22">
-        <v>32.38618354142574</v>
+        <v>32.4172374093594</v>
       </c>
       <c r="E22">
-        <v>-11</v>
+        <v>-10.67</v>
       </c>
       <c r="F22">
-        <v>6.600000000000001</v>
+        <v>6.930000000000001</v>
       </c>
       <c r="G22">
         <v>1.29</v>
@@ -3085,28 +3085,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M22">
-        <v>0.33198</v>
+        <v>0.348579</v>
       </c>
       <c r="N22">
-        <v>4.690264897959184</v>
+        <v>4.673665897959184</v>
       </c>
       <c r="O22">
-        <v>0.9380529795918369</v>
+        <v>0.9347331795918369</v>
       </c>
       <c r="P22">
-        <v>3.752211918367347</v>
+        <v>3.738932718367347</v>
       </c>
       <c r="Q22">
-        <v>3.842211918367347</v>
+        <v>3.828932718367347</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0791378770324362</v>
+        <v>0.07948954240197667</v>
       </c>
       <c r="T22">
-        <v>0.632407208197605</v>
+        <v>0.6390781703093941</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.12815500319051</v>
+        <v>14.40776666970524</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07124713849756156</v>
+        <v>0.07113597536917417</v>
       </c>
       <c r="C23">
-        <v>26.7772374093594</v>
+        <v>26.47835088717399</v>
       </c>
       <c r="D23">
-        <v>32.4172374093594</v>
+        <v>32.44835088717399</v>
       </c>
       <c r="E23">
-        <v>-10.67</v>
+        <v>-10.34</v>
       </c>
       <c r="F23">
-        <v>6.93</v>
+        <v>7.26</v>
       </c>
       <c r="G23">
         <v>1.29</v>
@@ -3167,28 +3167,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M23">
-        <v>0.348579</v>
+        <v>0.3651779999999999</v>
       </c>
       <c r="N23">
-        <v>4.673665897959184</v>
+        <v>4.657066897959184</v>
       </c>
       <c r="O23">
-        <v>0.9347331795918369</v>
+        <v>0.9314133795918368</v>
       </c>
       <c r="P23">
-        <v>3.738932718367347</v>
+        <v>3.725653518367347</v>
       </c>
       <c r="Q23">
-        <v>3.828932718367347</v>
+        <v>3.815653518367347</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07948954240197667</v>
+        <v>0.07985022483227458</v>
       </c>
       <c r="T23">
-        <v>0.6390781703093941</v>
+        <v>0.6459201827317419</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.40776666970524</v>
+        <v>13.75286818471864</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07113597536917417</v>
+        <v>0.07102481224078679</v>
       </c>
       <c r="C24">
-        <v>26.47835088717399</v>
+        <v>26.17952414667185</v>
       </c>
       <c r="D24">
-        <v>32.44835088717399</v>
+        <v>32.47952414667185</v>
       </c>
       <c r="E24">
-        <v>-10.34</v>
+        <v>-10.01</v>
       </c>
       <c r="F24">
-        <v>7.26</v>
+        <v>7.590000000000001</v>
       </c>
       <c r="G24">
         <v>1.29</v>
@@ -3249,28 +3249,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M24">
-        <v>0.3651779999999999</v>
+        <v>0.381777</v>
       </c>
       <c r="N24">
-        <v>4.657066897959184</v>
+        <v>4.640467897959184</v>
       </c>
       <c r="O24">
-        <v>0.9314133795918368</v>
+        <v>0.9280935795918368</v>
       </c>
       <c r="P24">
-        <v>3.725653518367347</v>
+        <v>3.712374318367347</v>
       </c>
       <c r="Q24">
-        <v>3.815653518367347</v>
+        <v>3.802374318367347</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07985022483227458</v>
+        <v>0.08022027563738543</v>
       </c>
       <c r="T24">
-        <v>0.6459201827317419</v>
+        <v>0.6529399097624623</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.75286818471864</v>
+        <v>13.1549173940787</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07102481224078679</v>
+        <v>0.0712016491123994</v>
       </c>
       <c r="C25">
-        <v>26.17952414667185</v>
+        <v>25.79996223025701</v>
       </c>
       <c r="D25">
-        <v>32.47952414667185</v>
+        <v>32.42996223025701</v>
       </c>
       <c r="E25">
-        <v>-10.01</v>
+        <v>-9.68</v>
       </c>
       <c r="F25">
-        <v>7.590000000000001</v>
+        <v>7.920000000000001</v>
       </c>
       <c r="G25">
         <v>1.29</v>
@@ -3331,45 +3331,45 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M25">
-        <v>0.381777</v>
+        <v>0.410256</v>
       </c>
       <c r="N25">
-        <v>4.640467897959184</v>
+        <v>4.611988897959184</v>
       </c>
       <c r="O25">
-        <v>0.9280935795918368</v>
+        <v>0.9223977795918368</v>
       </c>
       <c r="P25">
-        <v>3.712374318367347</v>
+        <v>3.689591118367347</v>
       </c>
       <c r="Q25">
-        <v>3.802374318367347</v>
+        <v>3.779591118367347</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08022027563738543</v>
+        <v>0.08060006462157815</v>
       </c>
       <c r="T25">
-        <v>0.6529399097624623</v>
+        <v>0.6601443664518859</v>
       </c>
       <c r="U25">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>13.1549173940787</v>
+        <v>12.24173418050969</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07120164911239939</v>
+        <v>0.07110248598401199</v>
       </c>
       <c r="C26">
-        <v>25.79996223025701</v>
+        <v>25.49773595020691</v>
       </c>
       <c r="D26">
-        <v>32.42996223025701</v>
+        <v>32.45773595020691</v>
       </c>
       <c r="E26">
-        <v>-9.680000000000001</v>
+        <v>-9.350000000000001</v>
       </c>
       <c r="F26">
-        <v>7.92</v>
+        <v>8.25</v>
       </c>
       <c r="G26">
         <v>1.29</v>
@@ -3413,28 +3413,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M26">
-        <v>0.410256</v>
+        <v>0.42735</v>
       </c>
       <c r="N26">
-        <v>4.611988897959184</v>
+        <v>4.594894897959184</v>
       </c>
       <c r="O26">
-        <v>0.9223977795918368</v>
+        <v>0.9189789795918369</v>
       </c>
       <c r="P26">
-        <v>3.689591118367347</v>
+        <v>3.675915918367347</v>
       </c>
       <c r="Q26">
-        <v>3.779591118367347</v>
+        <v>3.765915918367347</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08060006462157814</v>
+        <v>0.08098998131201599</v>
       </c>
       <c r="T26">
-        <v>0.6601443664518858</v>
+        <v>0.6675409419863607</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>12.24173418050969</v>
+        <v>11.75206481328931</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07110248598401199</v>
+        <v>0.07100332285562459</v>
       </c>
       <c r="C27">
-        <v>25.49773595020691</v>
+        <v>25.19555728296046</v>
       </c>
       <c r="D27">
-        <v>32.45773595020691</v>
+        <v>32.48555728296046</v>
       </c>
       <c r="E27">
-        <v>-9.350000000000001</v>
+        <v>-9.020000000000001</v>
       </c>
       <c r="F27">
-        <v>8.25</v>
+        <v>8.58</v>
       </c>
       <c r="G27">
         <v>1.29</v>
@@ -3495,28 +3495,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M27">
-        <v>0.42735</v>
+        <v>0.444444</v>
       </c>
       <c r="N27">
-        <v>4.594894897959184</v>
+        <v>4.577800897959184</v>
       </c>
       <c r="O27">
-        <v>0.9189789795918369</v>
+        <v>0.9155601795918369</v>
       </c>
       <c r="P27">
-        <v>3.675915918367347</v>
+        <v>3.662240718367348</v>
       </c>
       <c r="Q27">
-        <v>3.765915918367347</v>
+        <v>3.752240718367347</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08098998131201599</v>
+        <v>0.08139043629138459</v>
       </c>
       <c r="T27">
-        <v>0.6675409419863607</v>
+        <v>0.6751374249677135</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.75206481328931</v>
+        <v>11.30006232047048</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07100332285562459</v>
+        <v>0.0709041597272372</v>
       </c>
       <c r="C28">
-        <v>25.19555728296046</v>
+        <v>24.89342635105747</v>
       </c>
       <c r="D28">
-        <v>32.48555728296046</v>
+        <v>32.51342635105748</v>
       </c>
       <c r="E28">
-        <v>-9.020000000000001</v>
+        <v>-8.690000000000001</v>
       </c>
       <c r="F28">
-        <v>8.58</v>
+        <v>8.91</v>
       </c>
       <c r="G28">
         <v>1.29</v>
@@ -3577,28 +3577,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M28">
-        <v>0.444444</v>
+        <v>0.461538</v>
       </c>
       <c r="N28">
-        <v>4.577800897959184</v>
+        <v>4.560706897959184</v>
       </c>
       <c r="O28">
-        <v>0.9155601795918369</v>
+        <v>0.9121413795918368</v>
       </c>
       <c r="P28">
-        <v>3.662240718367348</v>
+        <v>3.648565518367347</v>
       </c>
       <c r="Q28">
-        <v>3.752240718367347</v>
+        <v>3.738565518367347</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08139043629138459</v>
+        <v>0.08180186264005096</v>
       </c>
       <c r="T28">
-        <v>0.6751374249677135</v>
+        <v>0.682942030770473</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.30006232047048</v>
+        <v>10.88154149378639</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0709041597272372</v>
+        <v>0.07080499659884981</v>
       </c>
       <c r="C29">
-        <v>24.89342635105747</v>
+        <v>24.59134327745858</v>
       </c>
       <c r="D29">
-        <v>32.51342635105748</v>
+        <v>32.54134327745859</v>
       </c>
       <c r="E29">
-        <v>-8.690000000000001</v>
+        <v>-8.360000000000001</v>
       </c>
       <c r="F29">
-        <v>8.91</v>
+        <v>9.24</v>
       </c>
       <c r="G29">
         <v>1.29</v>
@@ -3659,28 +3659,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M29">
-        <v>0.461538</v>
+        <v>0.478632</v>
       </c>
       <c r="N29">
-        <v>4.560706897959184</v>
+        <v>4.543612897959184</v>
       </c>
       <c r="O29">
-        <v>0.9121413795918368</v>
+        <v>0.9087225795918368</v>
       </c>
       <c r="P29">
-        <v>3.648565518367347</v>
+        <v>3.634890318367347</v>
       </c>
       <c r="Q29">
-        <v>3.738565518367347</v>
+        <v>3.724890318367347</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08180186264005096</v>
+        <v>0.08222471749840252</v>
       </c>
       <c r="T29">
-        <v>0.682942030770473</v>
+        <v>0.6909634311788647</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.88154149378639</v>
+        <v>10.49291501186545</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07080499659884981</v>
+        <v>0.07070583347046241</v>
       </c>
       <c r="C30">
-        <v>24.59134327745858</v>
+        <v>24.28930818554714</v>
       </c>
       <c r="D30">
-        <v>32.54134327745859</v>
+        <v>32.56930818554714</v>
       </c>
       <c r="E30">
-        <v>-8.360000000000001</v>
+        <v>-8.030000000000001</v>
       </c>
       <c r="F30">
-        <v>9.24</v>
+        <v>9.57</v>
       </c>
       <c r="G30">
         <v>1.29</v>
@@ -3741,28 +3741,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M30">
-        <v>0.478632</v>
+        <v>0.495726</v>
       </c>
       <c r="N30">
-        <v>4.543612897959184</v>
+        <v>4.526518897959184</v>
       </c>
       <c r="O30">
-        <v>0.9087225795918368</v>
+        <v>0.9053037795918368</v>
       </c>
       <c r="P30">
-        <v>3.634890318367347</v>
+        <v>3.621215118367347</v>
       </c>
       <c r="Q30">
-        <v>3.724890318367347</v>
+        <v>3.711215118367347</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08222471749840252</v>
+        <v>0.08265948376121468</v>
       </c>
       <c r="T30">
-        <v>0.6909634311788647</v>
+        <v>0.6992107865283379</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.49291501186545</v>
+        <v>10.13109035628388</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07070583347046241</v>
+        <v>0.07101467034207502</v>
       </c>
       <c r="C31">
-        <v>24.28930818554714</v>
+        <v>23.87237120142087</v>
       </c>
       <c r="D31">
-        <v>32.56930818554714</v>
+        <v>32.48237120142087</v>
       </c>
       <c r="E31">
-        <v>-8.030000000000003</v>
+        <v>-7.700000000000001</v>
       </c>
       <c r="F31">
-        <v>9.569999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="G31">
         <v>1.29</v>
@@ -3823,45 +3823,45 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M31">
-        <v>0.4957259999999999</v>
+        <v>0.52965</v>
       </c>
       <c r="N31">
-        <v>4.526518897959184</v>
+        <v>4.492594897959184</v>
       </c>
       <c r="O31">
-        <v>0.9053037795918368</v>
+        <v>0.8985189795918368</v>
       </c>
       <c r="P31">
-        <v>3.621215118367347</v>
+        <v>3.594075918367347</v>
       </c>
       <c r="Q31">
-        <v>3.711215118367347</v>
+        <v>3.684075918367347</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08265948376121468</v>
+        <v>0.08310667191725003</v>
       </c>
       <c r="T31">
-        <v>0.6992107865283379</v>
+        <v>0.7076937806020818</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>10.13109035628388</v>
+        <v>9.482195597015357</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07101467034207502</v>
+        <v>0.07092910721368763</v>
       </c>
       <c r="C32">
-        <v>23.87237120142087</v>
+        <v>23.56641054270005</v>
       </c>
       <c r="D32">
-        <v>32.48237120142087</v>
+        <v>32.50641054270005</v>
       </c>
       <c r="E32">
-        <v>-7.700000000000001</v>
+        <v>-7.370000000000001</v>
       </c>
       <c r="F32">
-        <v>9.9</v>
+        <v>10.23</v>
       </c>
       <c r="G32">
         <v>1.29</v>
@@ -3905,28 +3905,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M32">
-        <v>0.52965</v>
+        <v>0.547305</v>
       </c>
       <c r="N32">
-        <v>4.492594897959184</v>
+        <v>4.474939897959184</v>
       </c>
       <c r="O32">
-        <v>0.8985189795918368</v>
+        <v>0.894987979591837</v>
       </c>
       <c r="P32">
-        <v>3.594075918367347</v>
+        <v>3.579951918367347</v>
       </c>
       <c r="Q32">
-        <v>3.684075918367347</v>
+        <v>3.669951918367347</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08310667191725003</v>
+        <v>0.08356682204882265</v>
       </c>
       <c r="T32">
-        <v>0.7076937806020818</v>
+        <v>0.716422658562021</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.482195597015357</v>
+        <v>9.176318319692282</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07092910721368763</v>
+        <v>0.07084354408530025</v>
       </c>
       <c r="C33">
-        <v>23.56641054270005</v>
+        <v>23.26048549208944</v>
       </c>
       <c r="D33">
-        <v>32.50641054270005</v>
+        <v>32.53048549208945</v>
       </c>
       <c r="E33">
-        <v>-7.370000000000001</v>
+        <v>-7.040000000000001</v>
       </c>
       <c r="F33">
-        <v>10.23</v>
+        <v>10.56</v>
       </c>
       <c r="G33">
         <v>1.29</v>
@@ -3987,28 +3987,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M33">
-        <v>0.547305</v>
+        <v>0.56496</v>
       </c>
       <c r="N33">
-        <v>4.474939897959184</v>
+        <v>4.457284897959184</v>
       </c>
       <c r="O33">
-        <v>0.894987979591837</v>
+        <v>0.8914569795918368</v>
       </c>
       <c r="P33">
-        <v>3.579951918367347</v>
+        <v>3.565827918367347</v>
       </c>
       <c r="Q33">
-        <v>3.669951918367347</v>
+        <v>3.655827918367347</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08356682204882265</v>
+        <v>0.08404050600779447</v>
       </c>
       <c r="T33">
-        <v>0.716422658562021</v>
+        <v>0.7254082682266645</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.176318319692282</v>
+        <v>8.889558372201897</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07084354408530025</v>
+        <v>0.07075798095691284</v>
       </c>
       <c r="C34">
-        <v>23.26048549208944</v>
+        <v>22.95459612876412</v>
       </c>
       <c r="D34">
-        <v>32.53048549208945</v>
+        <v>32.55459612876412</v>
       </c>
       <c r="E34">
-        <v>-7.040000000000001</v>
+        <v>-6.710000000000001</v>
       </c>
       <c r="F34">
-        <v>10.56</v>
+        <v>10.89</v>
       </c>
       <c r="G34">
         <v>1.29</v>
@@ -4069,28 +4069,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M34">
-        <v>0.56496</v>
+        <v>0.582615</v>
       </c>
       <c r="N34">
-        <v>4.457284897959184</v>
+        <v>4.439629897959184</v>
       </c>
       <c r="O34">
-        <v>0.8914569795918368</v>
+        <v>0.8879259795918369</v>
       </c>
       <c r="P34">
-        <v>3.565827918367347</v>
+        <v>3.551703918367347</v>
       </c>
       <c r="Q34">
-        <v>3.655827918367347</v>
+        <v>3.641703918367347</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08404050600779447</v>
+        <v>0.08452832978643708</v>
       </c>
       <c r="T34">
-        <v>0.7254082682266645</v>
+        <v>0.7346621050454765</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.889558372201897</v>
+        <v>8.620177815468509</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07075798095691284</v>
+        <v>0.07067241782852546</v>
       </c>
       <c r="C35">
-        <v>22.95459612876412</v>
+        <v>22.64874253213397</v>
       </c>
       <c r="D35">
-        <v>32.55459612876412</v>
+        <v>32.57874253213397</v>
       </c>
       <c r="E35">
-        <v>-6.710000000000001</v>
+        <v>-6.380000000000001</v>
       </c>
       <c r="F35">
-        <v>10.89</v>
+        <v>11.22</v>
       </c>
       <c r="G35">
         <v>1.29</v>
@@ -4151,28 +4151,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M35">
-        <v>0.582615</v>
+        <v>0.60027</v>
       </c>
       <c r="N35">
-        <v>4.439629897959184</v>
+        <v>4.421974897959184</v>
       </c>
       <c r="O35">
-        <v>0.8879259795918369</v>
+        <v>0.8843949795918369</v>
       </c>
       <c r="P35">
-        <v>3.551703918367347</v>
+        <v>3.537579918367347</v>
       </c>
       <c r="Q35">
-        <v>3.641703918367347</v>
+        <v>3.627579918367347</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08452832978643708</v>
+        <v>0.08503093610382645</v>
       </c>
       <c r="T35">
-        <v>0.7346621050454765</v>
+        <v>0.7441963611618281</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.620177815468509</v>
+        <v>8.36664317383708</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07067241782852546</v>
+        <v>0.07058685470013806</v>
       </c>
       <c r="C36">
-        <v>22.64874253213397</v>
+        <v>22.34292478184477</v>
       </c>
       <c r="D36">
-        <v>32.57874253213397</v>
+        <v>32.60292478184477</v>
       </c>
       <c r="E36">
-        <v>-6.380000000000001</v>
+        <v>-6.050000000000001</v>
       </c>
       <c r="F36">
-        <v>11.22</v>
+        <v>11.55</v>
       </c>
       <c r="G36">
         <v>1.29</v>
@@ -4233,28 +4233,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M36">
-        <v>0.60027</v>
+        <v>0.6179250000000001</v>
       </c>
       <c r="N36">
-        <v>4.421974897959184</v>
+        <v>4.404319897959184</v>
       </c>
       <c r="O36">
-        <v>0.8843949795918369</v>
+        <v>0.8808639795918367</v>
       </c>
       <c r="P36">
-        <v>3.537579918367347</v>
+        <v>3.523455918367347</v>
       </c>
       <c r="Q36">
-        <v>3.627579918367347</v>
+        <v>3.613455918367347</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08503093610382645</v>
+        <v>0.08554900723098163</v>
       </c>
       <c r="T36">
-        <v>0.7441963611618281</v>
+        <v>0.7540239790048368</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.36664317383708</v>
+        <v>8.127596226013162</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07058685470013806</v>
+        <v>0.07050129157175067</v>
       </c>
       <c r="C37">
-        <v>22.34292478184477</v>
+        <v>22.03714295777885</v>
       </c>
       <c r="D37">
-        <v>32.60292478184477</v>
+        <v>32.62714295777886</v>
       </c>
       <c r="E37">
-        <v>-6.050000000000001</v>
+        <v>-5.720000000000001</v>
       </c>
       <c r="F37">
-        <v>11.55</v>
+        <v>11.88</v>
       </c>
       <c r="G37">
         <v>1.29</v>
@@ -4315,28 +4315,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M37">
-        <v>0.6179250000000001</v>
+        <v>0.63558</v>
       </c>
       <c r="N37">
-        <v>4.404319897959184</v>
+        <v>4.386664897959184</v>
       </c>
       <c r="O37">
-        <v>0.8808639795918367</v>
+        <v>0.8773329795918369</v>
       </c>
       <c r="P37">
-        <v>3.523455918367347</v>
+        <v>3.509331918367347</v>
       </c>
       <c r="Q37">
-        <v>3.613455918367347</v>
+        <v>3.599331918367347</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08554900723098163</v>
+        <v>0.08608326808086042</v>
       </c>
       <c r="T37">
-        <v>0.7540239790048368</v>
+        <v>0.7641587099054394</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.127596226013162</v>
+        <v>7.901829664179465</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07050129157175067</v>
+        <v>0.07041572844336327</v>
       </c>
       <c r="C38">
-        <v>22.03714295777886</v>
+        <v>21.73139714005615</v>
       </c>
       <c r="D38">
-        <v>32.62714295777886</v>
+        <v>32.65139714005615</v>
       </c>
       <c r="E38">
-        <v>-5.720000000000002</v>
+        <v>-5.390000000000002</v>
       </c>
       <c r="F38">
-        <v>11.88</v>
+        <v>12.21</v>
       </c>
       <c r="G38">
         <v>1.29</v>
@@ -4397,28 +4397,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M38">
-        <v>0.6355799999999999</v>
+        <v>0.6532349999999999</v>
       </c>
       <c r="N38">
-        <v>4.386664897959184</v>
+        <v>4.369009897959184</v>
       </c>
       <c r="O38">
-        <v>0.8773329795918369</v>
+        <v>0.8738019795918369</v>
       </c>
       <c r="P38">
-        <v>3.509331918367347</v>
+        <v>3.495207918367348</v>
       </c>
       <c r="Q38">
-        <v>3.599331918367347</v>
+        <v>3.585207918367348</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08608326808086042</v>
+        <v>0.08663448959264011</v>
       </c>
       <c r="T38">
-        <v>0.7641587099054393</v>
+        <v>0.7746151782949501</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.901829664179465</v>
+        <v>7.688266700282724</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07041572844336327</v>
+        <v>0.07057336531497588</v>
       </c>
       <c r="C39">
-        <v>21.73139714005615</v>
+        <v>21.35674049106329</v>
       </c>
       <c r="D39">
-        <v>32.65139714005615</v>
+        <v>32.60674049106329</v>
       </c>
       <c r="E39">
-        <v>-5.390000000000002</v>
+        <v>-5.06</v>
       </c>
       <c r="F39">
-        <v>12.21</v>
+        <v>12.54</v>
       </c>
       <c r="G39">
         <v>1.29</v>
@@ -4479,45 +4479,45 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M39">
-        <v>0.6532349999999999</v>
+        <v>0.680922</v>
       </c>
       <c r="N39">
-        <v>4.369009897959184</v>
+        <v>4.341322897959184</v>
       </c>
       <c r="O39">
-        <v>0.8738019795918369</v>
+        <v>0.8682645795918369</v>
       </c>
       <c r="P39">
-        <v>3.495207918367348</v>
+        <v>3.473058318367348</v>
       </c>
       <c r="Q39">
-        <v>3.585207918367348</v>
+        <v>3.563058318367347</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08663448959264011</v>
+        <v>0.08720349244350947</v>
       </c>
       <c r="T39">
-        <v>0.7746151782949501</v>
+        <v>0.7854089521163803</v>
       </c>
       <c r="U39">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>7.688266700282724</v>
+        <v>7.375653742953208</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07057336531497588</v>
+        <v>0.07049420218658849</v>
       </c>
       <c r="C40">
-        <v>21.35674049106329</v>
+        <v>21.04915118366535</v>
       </c>
       <c r="D40">
-        <v>32.60674049106329</v>
+        <v>32.62915118366535</v>
       </c>
       <c r="E40">
-        <v>-5.06</v>
+        <v>-4.73</v>
       </c>
       <c r="F40">
-        <v>12.54</v>
+        <v>12.87</v>
       </c>
       <c r="G40">
         <v>1.29</v>
@@ -4561,28 +4561,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M40">
-        <v>0.680922</v>
+        <v>0.698841</v>
       </c>
       <c r="N40">
-        <v>4.341322897959184</v>
+        <v>4.323403897959184</v>
       </c>
       <c r="O40">
-        <v>0.8682645795918369</v>
+        <v>0.8646807795918369</v>
       </c>
       <c r="P40">
-        <v>3.473058318367348</v>
+        <v>3.458723118367347</v>
       </c>
       <c r="Q40">
-        <v>3.563058318367347</v>
+        <v>3.548723118367347</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08720349244350947</v>
+        <v>0.08779115112555488</v>
       </c>
       <c r="T40">
-        <v>0.7854089521163803</v>
+        <v>0.7965566201614642</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.375653742953208</v>
+        <v>7.186534416210818</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07049420218658849</v>
+        <v>0.0704150390582011</v>
       </c>
       <c r="C41">
-        <v>21.04915118366535</v>
+        <v>20.74159270330274</v>
       </c>
       <c r="D41">
-        <v>32.62915118366535</v>
+        <v>32.65159270330274</v>
       </c>
       <c r="E41">
-        <v>-4.73</v>
+        <v>-4.4</v>
       </c>
       <c r="F41">
-        <v>12.87</v>
+        <v>13.2</v>
       </c>
       <c r="G41">
         <v>1.29</v>
@@ -4643,28 +4643,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M41">
-        <v>0.698841</v>
+        <v>0.7167600000000001</v>
       </c>
       <c r="N41">
-        <v>4.323403897959184</v>
+        <v>4.305484897959184</v>
       </c>
       <c r="O41">
-        <v>0.8646807795918369</v>
+        <v>0.8610969795918368</v>
       </c>
       <c r="P41">
-        <v>3.458723118367347</v>
+        <v>3.444387918367347</v>
       </c>
       <c r="Q41">
-        <v>3.548723118367347</v>
+        <v>3.534387918367347</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08779115112555488</v>
+        <v>0.08839839843033515</v>
       </c>
       <c r="T41">
-        <v>0.7965566201614642</v>
+        <v>0.8080758771413842</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.186534416210818</v>
+        <v>7.006871055805547</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0704150390582011</v>
+        <v>0.07033587592981369</v>
       </c>
       <c r="C42">
-        <v>20.74159270330274</v>
+        <v>20.43406511362544</v>
       </c>
       <c r="D42">
-        <v>32.65159270330274</v>
+        <v>32.67406511362544</v>
       </c>
       <c r="E42">
-        <v>-4.4</v>
+        <v>-4.07</v>
       </c>
       <c r="F42">
-        <v>13.2</v>
+        <v>13.53</v>
       </c>
       <c r="G42">
         <v>1.29</v>
@@ -4725,28 +4725,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M42">
-        <v>0.7167600000000001</v>
+        <v>0.7346790000000001</v>
       </c>
       <c r="N42">
-        <v>4.305484897959184</v>
+        <v>4.287565897959184</v>
       </c>
       <c r="O42">
-        <v>0.8610969795918368</v>
+        <v>0.8575131795918369</v>
       </c>
       <c r="P42">
-        <v>3.444387918367347</v>
+        <v>3.430052718367347</v>
       </c>
       <c r="Q42">
-        <v>3.534387918367347</v>
+        <v>3.520052718367347</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08839839843033515</v>
+        <v>0.08902623038951474</v>
       </c>
       <c r="T42">
-        <v>0.8080758771413842</v>
+        <v>0.8199856174087591</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.006871055805547</v>
+        <v>6.835971761761509</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07033587592981369</v>
+        <v>0.07025671280142631</v>
       </c>
       <c r="C43">
-        <v>20.43406511362544</v>
+        <v>20.12656847845878</v>
       </c>
       <c r="D43">
-        <v>32.67406511362544</v>
+        <v>32.69656847845878</v>
       </c>
       <c r="E43">
-        <v>-4.07</v>
+        <v>-3.74</v>
       </c>
       <c r="F43">
-        <v>13.53</v>
+        <v>13.86</v>
       </c>
       <c r="G43">
         <v>1.29</v>
@@ -4807,28 +4807,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M43">
-        <v>0.7346790000000001</v>
+        <v>0.7525980000000001</v>
       </c>
       <c r="N43">
-        <v>4.287565897959184</v>
+        <v>4.269646897959184</v>
       </c>
       <c r="O43">
-        <v>0.8575131795918369</v>
+        <v>0.8539293795918369</v>
       </c>
       <c r="P43">
-        <v>3.430052718367347</v>
+        <v>3.415717518367347</v>
       </c>
       <c r="Q43">
-        <v>3.520052718367347</v>
+        <v>3.505717518367347</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08902623038951474</v>
+        <v>0.08967571172659708</v>
       </c>
       <c r="T43">
-        <v>0.8199856174087591</v>
+        <v>0.8323060383750089</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.835971761761509</v>
+        <v>6.673210529338616</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07025671280142631</v>
+        <v>0.07017754967303892</v>
       </c>
       <c r="C44">
-        <v>20.12656847845878</v>
+        <v>19.81910286180405</v>
       </c>
       <c r="D44">
-        <v>32.69656847845878</v>
+        <v>32.71910286180405</v>
       </c>
       <c r="E44">
-        <v>-3.740000000000002</v>
+        <v>-3.410000000000002</v>
       </c>
       <c r="F44">
-        <v>13.86</v>
+        <v>14.19</v>
       </c>
       <c r="G44">
         <v>1.29</v>
@@ -4889,28 +4889,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M44">
-        <v>0.752598</v>
+        <v>0.770517</v>
       </c>
       <c r="N44">
-        <v>4.269646897959184</v>
+        <v>4.251727897959184</v>
       </c>
       <c r="O44">
-        <v>0.8539293795918369</v>
+        <v>0.8503455795918369</v>
       </c>
       <c r="P44">
-        <v>3.415717518367347</v>
+        <v>3.401382318367348</v>
       </c>
       <c r="Q44">
-        <v>3.505717518367347</v>
+        <v>3.491382318367347</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08967571172659707</v>
+        <v>0.09034798188252441</v>
       </c>
       <c r="T44">
-        <v>0.8323060383750087</v>
+        <v>0.8450587548137587</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.673210529338617</v>
+        <v>6.518019586795858</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07017754967303892</v>
+        <v>0.07009838654465153</v>
       </c>
       <c r="C45">
-        <v>19.81910286180405</v>
+        <v>19.51166832783909</v>
       </c>
       <c r="D45">
-        <v>32.71910286180405</v>
+        <v>32.74166832783909</v>
       </c>
       <c r="E45">
-        <v>-3.410000000000002</v>
+        <v>-3.080000000000002</v>
       </c>
       <c r="F45">
-        <v>14.19</v>
+        <v>14.52</v>
       </c>
       <c r="G45">
         <v>1.29</v>
@@ -4971,28 +4971,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M45">
-        <v>0.770517</v>
+        <v>0.788436</v>
       </c>
       <c r="N45">
-        <v>4.251727897959184</v>
+        <v>4.233808897959184</v>
       </c>
       <c r="O45">
-        <v>0.8503455795918369</v>
+        <v>0.8467617795918368</v>
       </c>
       <c r="P45">
-        <v>3.401382318367348</v>
+        <v>3.387047118367347</v>
       </c>
       <c r="Q45">
-        <v>3.491382318367347</v>
+        <v>3.477047118367347</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09034798188252441</v>
+        <v>0.09104426168687771</v>
       </c>
       <c r="T45">
-        <v>0.8450587548137587</v>
+        <v>0.8582669254110353</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.518019586795858</v>
+        <v>6.369882778005043</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07009838654465153</v>
+        <v>0.07001922341626413</v>
       </c>
       <c r="C46">
-        <v>19.51166832783909</v>
+        <v>19.20426494091893</v>
       </c>
       <c r="D46">
-        <v>32.74166832783909</v>
+        <v>32.76426494091893</v>
       </c>
       <c r="E46">
-        <v>-3.080000000000002</v>
+        <v>-2.750000000000002</v>
       </c>
       <c r="F46">
-        <v>14.52</v>
+        <v>14.85</v>
       </c>
       <c r="G46">
         <v>1.29</v>
@@ -5053,28 +5053,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M46">
-        <v>0.788436</v>
+        <v>0.806355</v>
       </c>
       <c r="N46">
-        <v>4.233808897959184</v>
+        <v>4.215889897959184</v>
       </c>
       <c r="O46">
-        <v>0.8467617795918368</v>
+        <v>0.8431779795918368</v>
       </c>
       <c r="P46">
-        <v>3.387047118367347</v>
+        <v>3.372711918367347</v>
       </c>
       <c r="Q46">
-        <v>3.477047118367347</v>
+        <v>3.462711918367347</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09104426168687771</v>
+        <v>0.09176586075684386</v>
       </c>
       <c r="T46">
-        <v>0.8582669254110353</v>
+        <v>0.8719553931209402</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.369882778005043</v>
+        <v>6.228329827382709</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07001922341626413</v>
+        <v>0.07030806028787673</v>
       </c>
       <c r="C47">
-        <v>19.20426494091893</v>
+        <v>18.79196861681548</v>
       </c>
       <c r="D47">
-        <v>32.76426494091893</v>
+        <v>32.68196861681548</v>
       </c>
       <c r="E47">
-        <v>-2.750000000000002</v>
+        <v>-2.42</v>
       </c>
       <c r="F47">
-        <v>14.85</v>
+        <v>15.18</v>
       </c>
       <c r="G47">
         <v>1.29</v>
@@ -5135,45 +5135,45 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M47">
-        <v>0.806355</v>
+        <v>0.8394540000000001</v>
       </c>
       <c r="N47">
-        <v>4.215889897959184</v>
+        <v>4.182790897959184</v>
       </c>
       <c r="O47">
-        <v>0.8431779795918368</v>
+        <v>0.8365581795918369</v>
       </c>
       <c r="P47">
-        <v>3.372711918367347</v>
+        <v>3.346232718367347</v>
       </c>
       <c r="Q47">
-        <v>3.462711918367347</v>
+        <v>3.436232718367347</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09176586075684386</v>
+        <v>0.09251418571829023</v>
       </c>
       <c r="T47">
-        <v>0.8719553931209402</v>
+        <v>0.8861508411163971</v>
       </c>
       <c r="U47">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>6.228329827382709</v>
+        <v>5.982751762406497</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07030806028787673</v>
+        <v>0.07023689715948934</v>
       </c>
       <c r="C48">
-        <v>18.79196861681548</v>
+        <v>18.48220623791082</v>
       </c>
       <c r="D48">
-        <v>32.68196861681548</v>
+        <v>32.70220623791082</v>
       </c>
       <c r="E48">
-        <v>-2.42</v>
+        <v>-2.09</v>
       </c>
       <c r="F48">
-        <v>15.18</v>
+        <v>15.51</v>
       </c>
       <c r="G48">
         <v>1.29</v>
@@ -5217,28 +5217,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M48">
-        <v>0.8394540000000001</v>
+        <v>0.8577030000000001</v>
       </c>
       <c r="N48">
-        <v>4.182790897959184</v>
+        <v>4.164541897959184</v>
       </c>
       <c r="O48">
-        <v>0.8365581795918369</v>
+        <v>0.8329083795918368</v>
       </c>
       <c r="P48">
-        <v>3.346232718367347</v>
+        <v>3.331633518367347</v>
       </c>
       <c r="Q48">
-        <v>3.436232718367347</v>
+        <v>3.421633518367347</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09251418571829023</v>
+        <v>0.09329074935752704</v>
       </c>
       <c r="T48">
-        <v>0.8861508411163971</v>
+        <v>0.9008819663947014</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.982751762406497</v>
+        <v>5.855459171716997</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07023689715948934</v>
+        <v>0.07016573403110195</v>
       </c>
       <c r="C49">
-        <v>18.48220623791082</v>
+        <v>18.17246893797748</v>
       </c>
       <c r="D49">
-        <v>32.70220623791082</v>
+        <v>32.72246893797749</v>
       </c>
       <c r="E49">
-        <v>-2.09</v>
+        <v>-1.76</v>
       </c>
       <c r="F49">
-        <v>15.51</v>
+        <v>15.84</v>
       </c>
       <c r="G49">
         <v>1.29</v>
@@ -5299,28 +5299,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M49">
-        <v>0.8577030000000001</v>
+        <v>0.8759520000000002</v>
       </c>
       <c r="N49">
-        <v>4.164541897959184</v>
+        <v>4.146292897959184</v>
       </c>
       <c r="O49">
-        <v>0.8329083795918368</v>
+        <v>0.8292585795918369</v>
       </c>
       <c r="P49">
-        <v>3.331633518367347</v>
+        <v>3.317034318367347</v>
       </c>
       <c r="Q49">
-        <v>3.421633518367347</v>
+        <v>3.407034318367347</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09329074935752704</v>
+        <v>0.0940971808290422</v>
       </c>
       <c r="T49">
-        <v>0.9008819663947014</v>
+        <v>0.916179673414479</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.855459171716997</v>
+        <v>5.733470438972893</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07016573403110195</v>
+        <v>0.07009457090271455</v>
       </c>
       <c r="C50">
-        <v>18.17246893797749</v>
+        <v>17.86275676366212</v>
       </c>
       <c r="D50">
-        <v>32.72246893797749</v>
+        <v>32.74275676366212</v>
       </c>
       <c r="E50">
-        <v>-1.760000000000002</v>
+        <v>-1.430000000000003</v>
       </c>
       <c r="F50">
-        <v>15.84</v>
+        <v>16.17</v>
       </c>
       <c r="G50">
         <v>1.29</v>
@@ -5381,28 +5381,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M50">
-        <v>0.8759520000000001</v>
+        <v>0.8942009999999999</v>
       </c>
       <c r="N50">
-        <v>4.146292897959184</v>
+        <v>4.128043897959184</v>
       </c>
       <c r="O50">
-        <v>0.8292585795918369</v>
+        <v>0.8256087795918369</v>
       </c>
       <c r="P50">
-        <v>3.317034318367347</v>
+        <v>3.302435118367347</v>
       </c>
       <c r="Q50">
-        <v>3.407034318367347</v>
+        <v>3.392435118367347</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0940971808290422</v>
+        <v>0.09493523706414617</v>
       </c>
       <c r="T50">
-        <v>0.916179673414479</v>
+        <v>0.9320772905134634</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.733470438972893</v>
+        <v>5.616460838177529</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07009457090271455</v>
+        <v>0.07002340777432715</v>
       </c>
       <c r="C51">
-        <v>17.86275676366212</v>
+        <v>17.55306976172714</v>
       </c>
       <c r="D51">
-        <v>32.74275676366212</v>
+        <v>32.76306976172714</v>
       </c>
       <c r="E51">
-        <v>-1.430000000000003</v>
+        <v>-1.100000000000001</v>
       </c>
       <c r="F51">
-        <v>16.17</v>
+        <v>16.5</v>
       </c>
       <c r="G51">
         <v>1.29</v>
@@ -5463,28 +5463,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M51">
-        <v>0.8942009999999999</v>
+        <v>0.91245</v>
       </c>
       <c r="N51">
-        <v>4.128043897959184</v>
+        <v>4.109794897959184</v>
       </c>
       <c r="O51">
-        <v>0.8256087795918369</v>
+        <v>0.8219589795918369</v>
       </c>
       <c r="P51">
-        <v>3.302435118367347</v>
+        <v>3.287835918367347</v>
       </c>
       <c r="Q51">
-        <v>3.392435118367347</v>
+        <v>3.377835918367347</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09493523706414617</v>
+        <v>0.09580681554865431</v>
       </c>
       <c r="T51">
-        <v>0.9320772905134634</v>
+        <v>0.9486108122964074</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.616460838177529</v>
+        <v>5.504131621413978</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07002340777432715</v>
+        <v>0.06995224464593976</v>
       </c>
       <c r="C52">
-        <v>17.55306976172714</v>
+        <v>17.24340797905104</v>
       </c>
       <c r="D52">
-        <v>32.76306976172714</v>
+        <v>32.78340797905104</v>
       </c>
       <c r="E52">
-        <v>-1.100000000000001</v>
+        <v>-0.7699999999999996</v>
       </c>
       <c r="F52">
-        <v>16.5</v>
+        <v>16.83</v>
       </c>
       <c r="G52">
         <v>1.29</v>
@@ -5545,28 +5545,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M52">
-        <v>0.91245</v>
+        <v>0.9306990000000002</v>
       </c>
       <c r="N52">
-        <v>4.109794897959184</v>
+        <v>4.091545897959184</v>
       </c>
       <c r="O52">
-        <v>0.8219589795918369</v>
+        <v>0.8183091795918369</v>
       </c>
       <c r="P52">
-        <v>3.287835918367347</v>
+        <v>3.273236718367348</v>
       </c>
       <c r="Q52">
-        <v>3.377835918367347</v>
+        <v>3.363236718367347</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09580681554865431</v>
+        <v>0.09671396866518318</v>
       </c>
       <c r="T52">
-        <v>0.9486108122964074</v>
+        <v>0.9658191717031451</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.504131621413978</v>
+        <v>5.396207471974487</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06995224464593976</v>
+        <v>0.06988108151755236</v>
       </c>
       <c r="C53">
-        <v>17.24340797905104</v>
+        <v>16.93377146262882</v>
       </c>
       <c r="D53">
-        <v>32.78340797905104</v>
+        <v>32.80377146262882</v>
       </c>
       <c r="E53">
-        <v>-0.7699999999999996</v>
+        <v>-0.4400000000000013</v>
       </c>
       <c r="F53">
-        <v>16.83</v>
+        <v>17.16</v>
       </c>
       <c r="G53">
         <v>1.29</v>
@@ -5627,28 +5627,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M53">
-        <v>0.9306990000000002</v>
+        <v>0.948948</v>
       </c>
       <c r="N53">
-        <v>4.091545897959184</v>
+        <v>4.073296897959184</v>
       </c>
       <c r="O53">
-        <v>0.8183091795918369</v>
+        <v>0.8146593795918369</v>
       </c>
       <c r="P53">
-        <v>3.273236718367348</v>
+        <v>3.258637518367347</v>
       </c>
       <c r="Q53">
-        <v>3.363236718367347</v>
+        <v>3.348637518367347</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09671396866518318</v>
+        <v>0.09765891982823409</v>
       </c>
       <c r="T53">
-        <v>0.9658191717031451</v>
+        <v>0.9837445460851633</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.396207471974487</v>
+        <v>5.292434251359595</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06988108151755236</v>
+        <v>0.06980991838916498</v>
       </c>
       <c r="C54">
-        <v>16.93377146262882</v>
+        <v>16.62416025957229</v>
       </c>
       <c r="D54">
-        <v>32.80377146262882</v>
+        <v>32.8241602595723</v>
       </c>
       <c r="E54">
-        <v>-0.4400000000000013</v>
+        <v>-0.1099999999999994</v>
       </c>
       <c r="F54">
-        <v>17.16</v>
+        <v>17.49</v>
       </c>
       <c r="G54">
         <v>1.29</v>
@@ -5709,28 +5709,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M54">
-        <v>0.948948</v>
+        <v>0.9671970000000002</v>
       </c>
       <c r="N54">
-        <v>4.073296897959184</v>
+        <v>4.055047897959184</v>
       </c>
       <c r="O54">
-        <v>0.8146593795918369</v>
+        <v>0.8110095795918367</v>
       </c>
       <c r="P54">
-        <v>3.258637518367347</v>
+        <v>3.244038318367347</v>
       </c>
       <c r="Q54">
-        <v>3.348637518367347</v>
+        <v>3.334038318367347</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09765891982823409</v>
+        <v>0.0986440816790744</v>
       </c>
       <c r="T54">
-        <v>0.9837445460851633</v>
+        <v>1.002432702355778</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.292434251359595</v>
+        <v>5.19257700133394</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06980991838916498</v>
+        <v>0.06973875526077758</v>
       </c>
       <c r="C55">
-        <v>16.62416025957229</v>
+        <v>16.31457441711051</v>
       </c>
       <c r="D55">
-        <v>32.8241602595723</v>
+        <v>32.84457441711051</v>
       </c>
       <c r="E55">
-        <v>-0.1099999999999994</v>
+        <v>0.2199999999999989</v>
       </c>
       <c r="F55">
-        <v>17.49</v>
+        <v>17.82</v>
       </c>
       <c r="G55">
         <v>1.29</v>
@@ -5791,28 +5791,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M55">
-        <v>0.9671970000000002</v>
+        <v>0.985446</v>
       </c>
       <c r="N55">
-        <v>4.055047897959184</v>
+        <v>4.036798897959184</v>
       </c>
       <c r="O55">
-        <v>0.8110095795918367</v>
+        <v>0.8073597795918368</v>
       </c>
       <c r="P55">
-        <v>3.244038318367347</v>
+        <v>3.229439118367347</v>
       </c>
       <c r="Q55">
-        <v>3.334038318367347</v>
+        <v>3.319439118367347</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.0986440816790744</v>
+        <v>0.09967207665386429</v>
       </c>
       <c r="T55">
-        <v>1.002432702355778</v>
+        <v>1.021933387159898</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.19257700133394</v>
+        <v>5.096418167975905</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06973875526077758</v>
+        <v>0.06966759213239018</v>
       </c>
       <c r="C56">
-        <v>16.31457441711051</v>
+        <v>16.00501398259003</v>
       </c>
       <c r="D56">
-        <v>32.84457441711051</v>
+        <v>32.86501398259004</v>
       </c>
       <c r="E56">
-        <v>0.2199999999999989</v>
+        <v>0.5500000000000007</v>
       </c>
       <c r="F56">
-        <v>17.82</v>
+        <v>18.15</v>
       </c>
       <c r="G56">
         <v>1.29</v>
@@ -5873,28 +5873,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M56">
-        <v>0.985446</v>
+        <v>1.003695</v>
       </c>
       <c r="N56">
-        <v>4.036798897959184</v>
+        <v>4.018549897959184</v>
       </c>
       <c r="O56">
-        <v>0.8073597795918368</v>
+        <v>0.8037099795918368</v>
       </c>
       <c r="P56">
-        <v>3.229439118367347</v>
+        <v>3.214839918367347</v>
       </c>
       <c r="Q56">
-        <v>3.319439118367347</v>
+        <v>3.304839918367347</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09967207665386429</v>
+        <v>0.1007457602942004</v>
       </c>
       <c r="T56">
-        <v>1.021933387159898</v>
+        <v>1.042300769066423</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.096418167975905</v>
+        <v>5.003756019467251</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06966759213239018</v>
+        <v>0.06959642900400279</v>
       </c>
       <c r="C57">
-        <v>16.00501398259003</v>
+        <v>15.6954790034754</v>
       </c>
       <c r="D57">
-        <v>32.86501398259004</v>
+        <v>32.8854790034754</v>
       </c>
       <c r="E57">
-        <v>0.5500000000000007</v>
+        <v>0.879999999999999</v>
       </c>
       <c r="F57">
-        <v>18.15</v>
+        <v>18.48</v>
       </c>
       <c r="G57">
         <v>1.29</v>
@@ -5955,28 +5955,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M57">
-        <v>1.003695</v>
+        <v>1.021944</v>
       </c>
       <c r="N57">
-        <v>4.018549897959184</v>
+        <v>4.000300897959184</v>
       </c>
       <c r="O57">
-        <v>0.8037099795918368</v>
+        <v>0.8000601795918367</v>
       </c>
       <c r="P57">
-        <v>3.214839918367347</v>
+        <v>3.200240718367347</v>
       </c>
       <c r="Q57">
-        <v>3.304839918367347</v>
+        <v>3.290240718367347</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1007457602942004</v>
+        <v>0.10186824773637</v>
       </c>
       <c r="T57">
-        <v>1.042300769066423</v>
+        <v>1.063593941059608</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.003756019467251</v>
+        <v>4.914403233405337</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06959642900400279</v>
+        <v>0.0695252658756154</v>
       </c>
       <c r="C58">
-        <v>15.6954790034754</v>
+        <v>15.38596952734942</v>
       </c>
       <c r="D58">
-        <v>32.8854790034754</v>
+        <v>32.90596952734943</v>
       </c>
       <c r="E58">
-        <v>0.879999999999999</v>
+        <v>1.210000000000001</v>
       </c>
       <c r="F58">
-        <v>18.48</v>
+        <v>18.81</v>
       </c>
       <c r="G58">
         <v>1.29</v>
@@ -6037,28 +6037,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M58">
-        <v>1.021944</v>
+        <v>1.040193</v>
       </c>
       <c r="N58">
-        <v>4.000300897959184</v>
+        <v>3.982051897959184</v>
       </c>
       <c r="O58">
-        <v>0.8000601795918367</v>
+        <v>0.7964103795918368</v>
       </c>
       <c r="P58">
-        <v>3.200240718367347</v>
+        <v>3.185641518367347</v>
       </c>
       <c r="Q58">
-        <v>3.290240718367347</v>
+        <v>3.275641518367347</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.10186824773637</v>
+        <v>0.10304294389678</v>
       </c>
       <c r="T58">
-        <v>1.063593941059608</v>
+        <v>1.0858774931455</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.914403233405337</v>
+        <v>4.828185632819277</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0695252658756154</v>
+        <v>0.06945410274722801</v>
       </c>
       <c r="C59">
-        <v>15.38596952734942</v>
+        <v>15.0764856019136</v>
       </c>
       <c r="D59">
-        <v>32.90596952734943</v>
+        <v>32.9264856019136</v>
       </c>
       <c r="E59">
-        <v>1.210000000000001</v>
+        <v>1.539999999999999</v>
       </c>
       <c r="F59">
-        <v>18.81</v>
+        <v>19.14</v>
       </c>
       <c r="G59">
         <v>1.29</v>
@@ -6119,28 +6119,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M59">
-        <v>1.040193</v>
+        <v>1.058442</v>
       </c>
       <c r="N59">
-        <v>3.982051897959184</v>
+        <v>3.963802897959184</v>
       </c>
       <c r="O59">
-        <v>0.7964103795918368</v>
+        <v>0.7927605795918368</v>
       </c>
       <c r="P59">
-        <v>3.185641518367347</v>
+        <v>3.171042318367347</v>
       </c>
       <c r="Q59">
-        <v>3.275641518367347</v>
+        <v>3.261042318367347</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.10304294389678</v>
+        <v>0.1042735779695905</v>
       </c>
       <c r="T59">
-        <v>1.0858774931455</v>
+        <v>1.109222166759291</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.828185632819277</v>
+        <v>4.744941052943084</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06945410274722799</v>
+        <v>0.06938293961884061</v>
       </c>
       <c r="C60">
-        <v>15.07648560191361</v>
+        <v>14.76702727498844</v>
       </c>
       <c r="D60">
-        <v>32.9264856019136</v>
+        <v>32.94702727498844</v>
       </c>
       <c r="E60">
-        <v>1.539999999999996</v>
+        <v>1.869999999999997</v>
       </c>
       <c r="F60">
-        <v>19.14</v>
+        <v>19.47</v>
       </c>
       <c r="G60">
         <v>1.29</v>
@@ -6201,28 +6201,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M60">
-        <v>1.058442</v>
+        <v>1.076691</v>
       </c>
       <c r="N60">
-        <v>3.963802897959184</v>
+        <v>3.945553897959184</v>
       </c>
       <c r="O60">
-        <v>0.7927605795918369</v>
+        <v>0.7891107795918368</v>
       </c>
       <c r="P60">
-        <v>3.171042318367348</v>
+        <v>3.156443118367347</v>
       </c>
       <c r="Q60">
-        <v>3.261042318367347</v>
+        <v>3.246443118367347</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1042735779695905</v>
+        <v>0.105564242972782</v>
       </c>
       <c r="T60">
-        <v>1.109222166759291</v>
+        <v>1.133705604939609</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.744941052943085</v>
+        <v>4.664518323232184</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06938293961884061</v>
+        <v>0.06931177649045321</v>
       </c>
       <c r="C61">
-        <v>14.76702727498844</v>
+        <v>14.45759459451388</v>
       </c>
       <c r="D61">
-        <v>32.94702727498844</v>
+        <v>32.96759459451388</v>
       </c>
       <c r="E61">
-        <v>1.869999999999997</v>
+        <v>2.199999999999999</v>
       </c>
       <c r="F61">
-        <v>19.47</v>
+        <v>19.8</v>
       </c>
       <c r="G61">
         <v>1.29</v>
@@ -6283,28 +6283,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M61">
-        <v>1.076691</v>
+        <v>1.09494</v>
       </c>
       <c r="N61">
-        <v>3.945553897959184</v>
+        <v>3.927304897959184</v>
       </c>
       <c r="O61">
-        <v>0.7891107795918368</v>
+        <v>0.7854609795918368</v>
       </c>
       <c r="P61">
-        <v>3.156443118367347</v>
+        <v>3.141843918367347</v>
       </c>
       <c r="Q61">
-        <v>3.246443118367347</v>
+        <v>3.231843918367347</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.105564242972782</v>
+        <v>0.106919441226133</v>
       </c>
       <c r="T61">
-        <v>1.133705604939609</v>
+        <v>1.159413215028942</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.664518323232184</v>
+        <v>4.586776351178314</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06931177649045321</v>
+        <v>0.06924061336206583</v>
       </c>
       <c r="C62">
-        <v>14.45759459451388</v>
+        <v>14.14818760854963</v>
       </c>
       <c r="D62">
-        <v>32.96759459451388</v>
+        <v>32.98818760854963</v>
       </c>
       <c r="E62">
-        <v>2.199999999999999</v>
+        <v>2.529999999999998</v>
       </c>
       <c r="F62">
-        <v>19.8</v>
+        <v>20.13</v>
       </c>
       <c r="G62">
         <v>1.29</v>
@@ -6365,28 +6365,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M62">
-        <v>1.09494</v>
+        <v>1.113189</v>
       </c>
       <c r="N62">
-        <v>3.927304897959184</v>
+        <v>3.909055897959184</v>
       </c>
       <c r="O62">
-        <v>0.7854609795918368</v>
+        <v>0.7818111795918368</v>
       </c>
       <c r="P62">
-        <v>3.141843918367347</v>
+        <v>3.127244718367347</v>
       </c>
       <c r="Q62">
-        <v>3.231843918367347</v>
+        <v>3.217244718367347</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.106919441226133</v>
+        <v>0.1083441368258098</v>
       </c>
       <c r="T62">
-        <v>1.159413215028942</v>
+        <v>1.186439164097216</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.586776351178314</v>
+        <v>4.511583296240966</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06924061336206583</v>
+        <v>0.07040945023367844</v>
       </c>
       <c r="C63">
-        <v>14.14818760854963</v>
+        <v>13.48317821507126</v>
       </c>
       <c r="D63">
-        <v>32.98818760854963</v>
+        <v>32.65317821507126</v>
       </c>
       <c r="E63">
-        <v>2.529999999999998</v>
+        <v>2.859999999999999</v>
       </c>
       <c r="F63">
-        <v>20.13</v>
+        <v>20.46</v>
       </c>
       <c r="G63">
         <v>1.29</v>
@@ -6447,45 +6447,45 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M63">
-        <v>1.113189</v>
+        <v>1.182588</v>
       </c>
       <c r="N63">
-        <v>3.909055897959184</v>
+        <v>3.839656897959184</v>
       </c>
       <c r="O63">
-        <v>0.7818111795918368</v>
+        <v>0.7679313795918369</v>
       </c>
       <c r="P63">
-        <v>3.127244718367347</v>
+        <v>3.071725518367347</v>
       </c>
       <c r="Q63">
-        <v>3.217244718367347</v>
+        <v>3.161725518367347</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1083441368258098</v>
+        <v>0.1098438164044169</v>
       </c>
       <c r="T63">
-        <v>1.186439164097216</v>
+        <v>1.214887531537504</v>
       </c>
       <c r="U63">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V63">
         <v>0.2</v>
       </c>
       <c r="W63">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>4.511583296240966</v>
+        <v>4.246825519926791</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07040945023367844</v>
+        <v>0.07035828710529103</v>
       </c>
       <c r="C64">
-        <v>13.48317821507126</v>
+        <v>13.16770000921542</v>
       </c>
       <c r="D64">
-        <v>32.65317821507126</v>
+        <v>32.66770000921542</v>
       </c>
       <c r="E64">
-        <v>2.859999999999999</v>
+        <v>3.189999999999998</v>
       </c>
       <c r="F64">
-        <v>20.46</v>
+        <v>20.79</v>
       </c>
       <c r="G64">
         <v>1.29</v>
@@ -6529,28 +6529,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M64">
-        <v>1.182588</v>
+        <v>1.201662</v>
       </c>
       <c r="N64">
-        <v>3.839656897959184</v>
+        <v>3.820582897959184</v>
       </c>
       <c r="O64">
-        <v>0.7679313795918369</v>
+        <v>0.7641165795918369</v>
       </c>
       <c r="P64">
-        <v>3.071725518367347</v>
+        <v>3.056466318367348</v>
       </c>
       <c r="Q64">
-        <v>3.161725518367347</v>
+        <v>3.146466318367347</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1098438164044169</v>
+        <v>0.1114245597440298</v>
       </c>
       <c r="T64">
-        <v>1.214887531537504</v>
+        <v>1.244873648569159</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.246825519926791</v>
+        <v>4.179415591039064</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07035828710529103</v>
+        <v>0.07030712397690364</v>
       </c>
       <c r="C65">
-        <v>13.16770000921542</v>
+        <v>12.85223472561362</v>
       </c>
       <c r="D65">
-        <v>32.66770000921542</v>
+        <v>32.68223472561362</v>
       </c>
       <c r="E65">
-        <v>3.189999999999998</v>
+        <v>3.52</v>
       </c>
       <c r="F65">
-        <v>20.79</v>
+        <v>21.12</v>
       </c>
       <c r="G65">
         <v>1.29</v>
@@ -6611,28 +6611,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M65">
-        <v>1.201662</v>
+        <v>1.220736</v>
       </c>
       <c r="N65">
-        <v>3.820582897959184</v>
+        <v>3.801508897959184</v>
       </c>
       <c r="O65">
-        <v>0.7641165795918369</v>
+        <v>0.7603017795918369</v>
       </c>
       <c r="P65">
-        <v>3.056466318367348</v>
+        <v>3.041207118367347</v>
       </c>
       <c r="Q65">
-        <v>3.146466318367347</v>
+        <v>3.131207118367347</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1114245597440298</v>
+        <v>0.1130931221580657</v>
       </c>
       <c r="T65">
-        <v>1.244873648569159</v>
+        <v>1.276525660991462</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.179415591039064</v>
+        <v>4.114112222429078</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07030712397690364</v>
+        <v>0.07025596084851625</v>
       </c>
       <c r="C66">
-        <v>12.85223472561362</v>
+        <v>12.53678238152189</v>
       </c>
       <c r="D66">
-        <v>32.68223472561362</v>
+        <v>32.69678238152189</v>
       </c>
       <c r="E66">
-        <v>3.52</v>
+        <v>3.849999999999998</v>
       </c>
       <c r="F66">
-        <v>21.12</v>
+        <v>21.45</v>
       </c>
       <c r="G66">
         <v>1.29</v>
@@ -6693,28 +6693,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M66">
-        <v>1.220736</v>
+        <v>1.23981</v>
       </c>
       <c r="N66">
-        <v>3.801508897959184</v>
+        <v>3.782434897959184</v>
       </c>
       <c r="O66">
-        <v>0.7603017795918369</v>
+        <v>0.7564869795918368</v>
       </c>
       <c r="P66">
-        <v>3.041207118367347</v>
+        <v>3.025947918367347</v>
       </c>
       <c r="Q66">
-        <v>3.131207118367347</v>
+        <v>3.115947918367347</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1130931221580657</v>
+        <v>0.1148570309957607</v>
       </c>
       <c r="T66">
-        <v>1.276525660991462</v>
+        <v>1.309986359837896</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.114112222429078</v>
+        <v>4.050818188237862</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07025596084851625</v>
+        <v>0.07205279772012885</v>
       </c>
       <c r="C67">
-        <v>12.53678238152189</v>
+        <v>11.70351220633998</v>
       </c>
       <c r="D67">
-        <v>32.69678238152189</v>
+        <v>32.19351220633998</v>
       </c>
       <c r="E67">
-        <v>3.849999999999998</v>
+        <v>4.18</v>
       </c>
       <c r="F67">
-        <v>21.45</v>
+        <v>21.78</v>
       </c>
       <c r="G67">
         <v>1.29</v>
@@ -6775,45 +6775,45 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M67">
-        <v>1.23981</v>
+        <v>1.335114</v>
       </c>
       <c r="N67">
-        <v>3.782434897959184</v>
+        <v>3.687130897959184</v>
       </c>
       <c r="O67">
-        <v>0.7564869795918368</v>
+        <v>0.7374261795918369</v>
       </c>
       <c r="P67">
-        <v>3.025947918367347</v>
+        <v>2.949704718367347</v>
       </c>
       <c r="Q67">
-        <v>3.115947918367347</v>
+        <v>3.039704718367347</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1148570309957607</v>
+        <v>0.1167246991768496</v>
       </c>
       <c r="T67">
-        <v>1.309986359837896</v>
+        <v>1.345415335087062</v>
       </c>
       <c r="U67">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V67">
         <v>0.2</v>
       </c>
       <c r="W67">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>4.050818188237862</v>
+        <v>3.761659976570678</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07205279772012885</v>
+        <v>0.07202963459174147</v>
       </c>
       <c r="C68">
-        <v>11.70351220633998</v>
+        <v>11.37990130039024</v>
       </c>
       <c r="D68">
-        <v>32.19351220633998</v>
+        <v>32.19990130039024</v>
       </c>
       <c r="E68">
-        <v>4.18</v>
+        <v>4.510000000000002</v>
       </c>
       <c r="F68">
-        <v>21.78</v>
+        <v>22.11</v>
       </c>
       <c r="G68">
         <v>1.29</v>
@@ -6857,28 +6857,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M68">
-        <v>1.335114</v>
+        <v>1.355343</v>
       </c>
       <c r="N68">
-        <v>3.687130897959184</v>
+        <v>3.666901897959184</v>
       </c>
       <c r="O68">
-        <v>0.7374261795918369</v>
+        <v>0.7333803795918368</v>
       </c>
       <c r="P68">
-        <v>2.949704718367347</v>
+        <v>2.933521518367347</v>
       </c>
       <c r="Q68">
-        <v>3.039704718367347</v>
+        <v>3.023521518367347</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1167246991768496</v>
+        <v>0.1187055593689135</v>
       </c>
       <c r="T68">
-        <v>1.345415335087062</v>
+        <v>1.382991520957389</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.761659976570678</v>
+        <v>3.705515797815891</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07202963459174147</v>
+        <v>0.07200647146335407</v>
       </c>
       <c r="C69">
-        <v>11.37990130039024</v>
+        <v>11.05629293089105</v>
       </c>
       <c r="D69">
-        <v>32.19990130039024</v>
+        <v>32.20629293089105</v>
       </c>
       <c r="E69">
-        <v>4.510000000000002</v>
+        <v>4.84</v>
       </c>
       <c r="F69">
-        <v>22.11</v>
+        <v>22.44</v>
       </c>
       <c r="G69">
         <v>1.29</v>
@@ -6939,28 +6939,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M69">
-        <v>1.355343</v>
+        <v>1.375572</v>
       </c>
       <c r="N69">
-        <v>3.666901897959184</v>
+        <v>3.646672897959184</v>
       </c>
       <c r="O69">
-        <v>0.7333803795918368</v>
+        <v>0.7293345795918369</v>
       </c>
       <c r="P69">
-        <v>2.933521518367347</v>
+        <v>2.917338318367347</v>
       </c>
       <c r="Q69">
-        <v>3.023521518367347</v>
+        <v>3.007338318367347</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1187055593689135</v>
+        <v>0.1208102233229815</v>
       </c>
       <c r="T69">
-        <v>1.382991520957389</v>
+        <v>1.422916218444611</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.705515797815891</v>
+        <v>3.651022918436246</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07200647146335407</v>
+        <v>0.07198330833496668</v>
       </c>
       <c r="C70">
-        <v>11.05629293089105</v>
+        <v>10.73268709935313</v>
       </c>
       <c r="D70">
-        <v>32.20629293089105</v>
+        <v>32.21268709935313</v>
       </c>
       <c r="E70">
-        <v>4.84</v>
+        <v>5.170000000000002</v>
       </c>
       <c r="F70">
-        <v>22.44</v>
+        <v>22.77</v>
       </c>
       <c r="G70">
         <v>1.29</v>
@@ -7021,28 +7021,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M70">
-        <v>1.375572</v>
+        <v>1.395801</v>
       </c>
       <c r="N70">
-        <v>3.646672897959184</v>
+        <v>3.626443897959184</v>
       </c>
       <c r="O70">
-        <v>0.7293345795918369</v>
+        <v>0.7252887795918368</v>
       </c>
       <c r="P70">
-        <v>2.917338318367347</v>
+        <v>2.901155118367347</v>
       </c>
       <c r="Q70">
-        <v>3.007338318367347</v>
+        <v>2.991155118367347</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1208102233229815</v>
+        <v>0.1230506720482796</v>
       </c>
       <c r="T70">
-        <v>1.422916218444611</v>
+        <v>1.465416702866494</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.651022918436246</v>
+        <v>3.598109542806735</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07198330833496668</v>
+        <v>0.07196014520657928</v>
       </c>
       <c r="C71">
-        <v>10.73268709935313</v>
+        <v>10.40908380728844</v>
       </c>
       <c r="D71">
-        <v>32.21268709935313</v>
+        <v>32.21908380728844</v>
       </c>
       <c r="E71">
-        <v>5.170000000000002</v>
+        <v>5.5</v>
       </c>
       <c r="F71">
-        <v>22.77</v>
+        <v>23.1</v>
       </c>
       <c r="G71">
         <v>1.29</v>
@@ -7103,28 +7103,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M71">
-        <v>1.395801</v>
+        <v>1.41603</v>
       </c>
       <c r="N71">
-        <v>3.626443897959184</v>
+        <v>3.606214897959184</v>
       </c>
       <c r="O71">
-        <v>0.7252887795918368</v>
+        <v>0.7212429795918368</v>
       </c>
       <c r="P71">
-        <v>2.901155118367347</v>
+        <v>2.884971918367347</v>
       </c>
       <c r="Q71">
-        <v>2.991155118367347</v>
+        <v>2.974971918367347</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1230506720482796</v>
+        <v>0.1254404840219309</v>
       </c>
       <c r="T71">
-        <v>1.465416702866494</v>
+        <v>1.510750552916501</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.598109542806735</v>
+        <v>3.546707977909496</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07196014520657928</v>
+        <v>0.0735273820781919</v>
       </c>
       <c r="C72">
-        <v>10.40908380728844</v>
+        <v>9.651930382490132</v>
       </c>
       <c r="D72">
-        <v>32.21908380728844</v>
+        <v>31.79193038249014</v>
       </c>
       <c r="E72">
-        <v>5.5</v>
+        <v>5.830000000000002</v>
       </c>
       <c r="F72">
-        <v>23.1</v>
+        <v>23.43</v>
       </c>
       <c r="G72">
         <v>1.29</v>
@@ -7185,45 +7185,45 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M72">
-        <v>1.41603</v>
+        <v>1.501863</v>
       </c>
       <c r="N72">
-        <v>3.606214897959184</v>
+        <v>3.520381897959184</v>
       </c>
       <c r="O72">
-        <v>0.7212429795918368</v>
+        <v>0.7040763795918368</v>
       </c>
       <c r="P72">
-        <v>2.884971918367347</v>
+        <v>2.816305518367347</v>
       </c>
       <c r="Q72">
-        <v>2.974971918367347</v>
+        <v>2.906305518367347</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1254404840219309</v>
+        <v>0.1279951106144548</v>
       </c>
       <c r="T72">
-        <v>1.510750552916501</v>
+        <v>1.559210875383751</v>
       </c>
       <c r="U72">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V72">
         <v>0.2</v>
       </c>
       <c r="W72">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y72">
-        <v>3.546707977909496</v>
+        <v>3.344010004880061</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0735273820781919</v>
+        <v>0.0735266189498045</v>
       </c>
       <c r="C73">
-        <v>9.651930382490136</v>
+        <v>9.322135618412347</v>
       </c>
       <c r="D73">
-        <v>31.79193038249014</v>
+        <v>31.79213561841234</v>
       </c>
       <c r="E73">
-        <v>5.829999999999998</v>
+        <v>6.159999999999997</v>
       </c>
       <c r="F73">
-        <v>23.43</v>
+        <v>23.76</v>
       </c>
       <c r="G73">
         <v>1.29</v>
@@ -7267,28 +7267,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M73">
-        <v>1.501863</v>
+        <v>1.523016</v>
       </c>
       <c r="N73">
-        <v>3.520381897959184</v>
+        <v>3.499228897959184</v>
       </c>
       <c r="O73">
-        <v>0.7040763795918368</v>
+        <v>0.6998457795918368</v>
       </c>
       <c r="P73">
-        <v>2.816305518367347</v>
+        <v>2.799383118367347</v>
       </c>
       <c r="Q73">
-        <v>2.906305518367347</v>
+        <v>2.889383118367347</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1279951106144548</v>
+        <v>0.130732210535016</v>
       </c>
       <c r="T73">
-        <v>1.55921087538375</v>
+        <v>1.611132649455803</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.344010004880061</v>
+        <v>3.29756542147895</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0735266189498045</v>
+        <v>0.0735258558214171</v>
       </c>
       <c r="C74">
-        <v>9.322135618412347</v>
+        <v>8.992340856984402</v>
       </c>
       <c r="D74">
-        <v>31.79213561841234</v>
+        <v>31.7923408569844</v>
       </c>
       <c r="E74">
-        <v>6.159999999999997</v>
+        <v>6.489999999999998</v>
       </c>
       <c r="F74">
-        <v>23.76</v>
+        <v>24.09</v>
       </c>
       <c r="G74">
         <v>1.29</v>
@@ -7349,28 +7349,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M74">
-        <v>1.523016</v>
+        <v>1.544169</v>
       </c>
       <c r="N74">
-        <v>3.499228897959184</v>
+        <v>3.478075897959184</v>
       </c>
       <c r="O74">
-        <v>0.6998457795918368</v>
+        <v>0.6956151795918368</v>
       </c>
       <c r="P74">
-        <v>2.799383118367347</v>
+        <v>2.782460718367347</v>
       </c>
       <c r="Q74">
-        <v>2.889383118367347</v>
+        <v>2.872460718367347</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.130732210535016</v>
+        <v>0.1336720585978411</v>
       </c>
       <c r="T74">
-        <v>1.611132649455803</v>
+        <v>1.666900480866526</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.29756542147895</v>
+        <v>3.252393292417594</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0735258558214171</v>
+        <v>0.0735250926930297</v>
       </c>
       <c r="C75">
-        <v>8.992340856984402</v>
+        <v>8.662546098206366</v>
       </c>
       <c r="D75">
-        <v>31.7923408569844</v>
+        <v>31.79254609820636</v>
       </c>
       <c r="E75">
-        <v>6.489999999999998</v>
+        <v>6.819999999999997</v>
       </c>
       <c r="F75">
-        <v>24.09</v>
+        <v>24.42</v>
       </c>
       <c r="G75">
         <v>1.29</v>
@@ -7431,28 +7431,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M75">
-        <v>1.544169</v>
+        <v>1.565322</v>
       </c>
       <c r="N75">
-        <v>3.478075897959184</v>
+        <v>3.456922897959184</v>
       </c>
       <c r="O75">
-        <v>0.6956151795918368</v>
+        <v>0.6913845795918369</v>
       </c>
       <c r="P75">
-        <v>2.782460718367347</v>
+        <v>2.765538318367347</v>
       </c>
       <c r="Q75">
-        <v>2.872460718367347</v>
+        <v>2.855538318367347</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1336720585978411</v>
+        <v>0.136838048819345</v>
       </c>
       <c r="T75">
-        <v>1.666900480866526</v>
+        <v>1.72695814546269</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.252393292417594</v>
+        <v>3.208442031709248</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0735250926930297</v>
+        <v>0.07352432956464232</v>
       </c>
       <c r="C76">
-        <v>8.662546098206366</v>
+        <v>8.332751342078289</v>
       </c>
       <c r="D76">
-        <v>31.79254609820636</v>
+        <v>31.79275134207829</v>
       </c>
       <c r="E76">
-        <v>6.819999999999997</v>
+        <v>7.149999999999999</v>
       </c>
       <c r="F76">
-        <v>24.42</v>
+        <v>24.75</v>
       </c>
       <c r="G76">
         <v>1.29</v>
@@ -7513,28 +7513,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M76">
-        <v>1.565322</v>
+        <v>1.586475</v>
       </c>
       <c r="N76">
-        <v>3.456922897959184</v>
+        <v>3.435769897959184</v>
       </c>
       <c r="O76">
-        <v>0.6913845795918369</v>
+        <v>0.6871539795918369</v>
       </c>
       <c r="P76">
-        <v>2.765538318367347</v>
+        <v>2.748615918367347</v>
       </c>
       <c r="Q76">
-        <v>2.855538318367347</v>
+        <v>2.838615918367347</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.136838048819345</v>
+        <v>0.1402573182585692</v>
       </c>
       <c r="T76">
-        <v>1.72695814546269</v>
+        <v>1.791820423226548</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.208442031709248</v>
+        <v>3.165662804619791</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07352432956464232</v>
+        <v>0.07352356643625492</v>
       </c>
       <c r="C77">
-        <v>8.332751342078289</v>
+        <v>8.002956588600231</v>
       </c>
       <c r="D77">
-        <v>31.79275134207829</v>
+        <v>31.79295658860023</v>
       </c>
       <c r="E77">
-        <v>7.149999999999999</v>
+        <v>7.48</v>
       </c>
       <c r="F77">
-        <v>24.75</v>
+        <v>25.08</v>
       </c>
       <c r="G77">
         <v>1.29</v>
@@ -7595,28 +7595,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M77">
-        <v>1.586475</v>
+        <v>1.607628</v>
       </c>
       <c r="N77">
-        <v>3.435769897959184</v>
+        <v>3.414616897959184</v>
       </c>
       <c r="O77">
-        <v>0.6871539795918369</v>
+        <v>0.6829233795918368</v>
       </c>
       <c r="P77">
-        <v>2.748615918367347</v>
+        <v>2.731693518367347</v>
       </c>
       <c r="Q77">
-        <v>2.838615918367347</v>
+        <v>2.821693518367347</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1402573182585692</v>
+        <v>0.1439615268177288</v>
       </c>
       <c r="T77">
-        <v>1.791820423226548</v>
+        <v>1.862087890804059</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.165662804619791</v>
+        <v>3.124009346664268</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07352356643625492</v>
+        <v>0.07352280330786753</v>
       </c>
       <c r="C78">
-        <v>8.002956588600231</v>
+        <v>7.673161837772238</v>
       </c>
       <c r="D78">
-        <v>31.79295658860023</v>
+        <v>31.79316183777224</v>
       </c>
       <c r="E78">
-        <v>7.48</v>
+        <v>7.809999999999999</v>
       </c>
       <c r="F78">
-        <v>25.08</v>
+        <v>25.41</v>
       </c>
       <c r="G78">
         <v>1.29</v>
@@ -7677,28 +7677,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M78">
-        <v>1.607628</v>
+        <v>1.628781</v>
       </c>
       <c r="N78">
-        <v>3.414616897959184</v>
+        <v>3.393463897959184</v>
       </c>
       <c r="O78">
-        <v>0.6829233795918368</v>
+        <v>0.6786927795918368</v>
       </c>
       <c r="P78">
-        <v>2.731693518367347</v>
+        <v>2.714771118367347</v>
       </c>
       <c r="Q78">
-        <v>2.821693518367347</v>
+        <v>2.804771118367347</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1439615268177288</v>
+        <v>0.1479878404689892</v>
       </c>
       <c r="T78">
-        <v>1.862087890804059</v>
+        <v>1.938465572953529</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.124009346664268</v>
+        <v>3.083437796707589</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07352280330786753</v>
+        <v>0.07352204017948014</v>
       </c>
       <c r="C79">
-        <v>7.673161837772238</v>
+        <v>7.343367089594359</v>
       </c>
       <c r="D79">
-        <v>31.79316183777224</v>
+        <v>31.79336708959436</v>
       </c>
       <c r="E79">
-        <v>7.809999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="F79">
-        <v>25.41</v>
+        <v>25.74</v>
       </c>
       <c r="G79">
         <v>1.29</v>
@@ -7759,28 +7759,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M79">
-        <v>1.628781</v>
+        <v>1.649934</v>
       </c>
       <c r="N79">
-        <v>3.393463897959184</v>
+        <v>3.372310897959184</v>
       </c>
       <c r="O79">
-        <v>0.6786927795918368</v>
+        <v>0.6744621795918369</v>
       </c>
       <c r="P79">
-        <v>2.714771118367347</v>
+        <v>2.697848718367347</v>
       </c>
       <c r="Q79">
-        <v>2.804771118367347</v>
+        <v>2.787848718367347</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1479878404689892</v>
+        <v>0.1523801826340006</v>
       </c>
       <c r="T79">
-        <v>1.938465572953529</v>
+        <v>2.02178668075295</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.083437796707589</v>
+        <v>3.043906542903645</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07352204017948014</v>
+        <v>0.07352127705109274</v>
       </c>
       <c r="C80">
-        <v>7.343367089594359</v>
+        <v>7.013572344066638</v>
       </c>
       <c r="D80">
-        <v>31.79336708959436</v>
+        <v>31.79357234406664</v>
       </c>
       <c r="E80">
-        <v>8.140000000000001</v>
+        <v>8.469999999999999</v>
       </c>
       <c r="F80">
-        <v>25.74</v>
+        <v>26.07</v>
       </c>
       <c r="G80">
         <v>1.29</v>
@@ -7841,28 +7841,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M80">
-        <v>1.649934</v>
+        <v>1.671087</v>
       </c>
       <c r="N80">
-        <v>3.372310897959184</v>
+        <v>3.351157897959184</v>
       </c>
       <c r="O80">
-        <v>0.6744621795918369</v>
+        <v>0.6702315795918369</v>
       </c>
       <c r="P80">
-        <v>2.697848718367347</v>
+        <v>2.680926318367347</v>
       </c>
       <c r="Q80">
-        <v>2.787848718367347</v>
+        <v>2.770926318367347</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1523801826340006</v>
+        <v>0.1571908431004416</v>
       </c>
       <c r="T80">
-        <v>2.02178668075295</v>
+        <v>2.113043132152316</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.043906542903645</v>
+        <v>3.005376080335245</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07352127705109274</v>
+        <v>0.07851251392270535</v>
       </c>
       <c r="C81">
-        <v>7.013572344066638</v>
+        <v>5.395487000394624</v>
       </c>
       <c r="D81">
-        <v>31.79357234406664</v>
+        <v>30.50548700039463</v>
       </c>
       <c r="E81">
-        <v>8.469999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F81">
-        <v>26.07</v>
+        <v>26.4</v>
       </c>
       <c r="G81">
         <v>1.29</v>
@@ -7923,45 +7923,45 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M81">
-        <v>1.671087</v>
+        <v>1.89816</v>
       </c>
       <c r="N81">
-        <v>3.351157897959184</v>
+        <v>3.124084897959184</v>
       </c>
       <c r="O81">
-        <v>0.6702315795918369</v>
+        <v>0.6248169795918368</v>
       </c>
       <c r="P81">
-        <v>2.680926318367347</v>
+        <v>2.499267918367347</v>
       </c>
       <c r="Q81">
-        <v>2.770926318367347</v>
+        <v>2.589267918367347</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1571908431004416</v>
+        <v>0.1624825696135268</v>
       </c>
       <c r="T81">
-        <v>2.113043132152316</v>
+        <v>2.213425228691618</v>
       </c>
       <c r="U81">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V81">
         <v>0.2</v>
       </c>
       <c r="W81">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y81">
-        <v>3.005376080335245</v>
+        <v>2.645849084354945</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07851251392270535</v>
+        <v>0.07857415079431795</v>
       </c>
       <c r="C82">
-        <v>5.395487000394624</v>
+        <v>5.050232483672868</v>
       </c>
       <c r="D82">
-        <v>30.50548700039463</v>
+        <v>30.49023248367287</v>
       </c>
       <c r="E82">
-        <v>8.800000000000001</v>
+        <v>9.129999999999999</v>
       </c>
       <c r="F82">
-        <v>26.4</v>
+        <v>26.73</v>
       </c>
       <c r="G82">
         <v>1.29</v>
@@ -8005,28 +8005,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M82">
-        <v>1.89816</v>
+        <v>1.921887</v>
       </c>
       <c r="N82">
-        <v>3.124084897959184</v>
+        <v>3.100357897959184</v>
       </c>
       <c r="O82">
-        <v>0.6248169795918368</v>
+        <v>0.6200715795918369</v>
       </c>
       <c r="P82">
-        <v>2.499267918367347</v>
+        <v>2.480286318367347</v>
       </c>
       <c r="Q82">
-        <v>2.589267918367347</v>
+        <v>2.570286318367347</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1624825696135268</v>
+        <v>0.1683313199700945</v>
       </c>
       <c r="T82">
-        <v>2.213425228691618</v>
+        <v>2.324373861708742</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.645849084354945</v>
+        <v>2.613184280844391</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07857415079431795</v>
+        <v>0.07863578766593056</v>
       </c>
       <c r="C83">
-        <v>5.050232483672868</v>
+        <v>4.704993215616039</v>
       </c>
       <c r="D83">
-        <v>30.49023248367287</v>
+        <v>30.47499321561604</v>
       </c>
       <c r="E83">
-        <v>9.129999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="F83">
-        <v>26.73</v>
+        <v>27.06</v>
       </c>
       <c r="G83">
         <v>1.29</v>
@@ -8087,28 +8087,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M83">
-        <v>1.921887</v>
+        <v>1.945614</v>
       </c>
       <c r="N83">
-        <v>3.100357897959184</v>
+        <v>3.076630897959184</v>
       </c>
       <c r="O83">
-        <v>0.6200715795918369</v>
+        <v>0.6153261795918368</v>
       </c>
       <c r="P83">
-        <v>2.480286318367347</v>
+        <v>2.461304718367347</v>
       </c>
       <c r="Q83">
-        <v>2.570286318367347</v>
+        <v>2.551304718367347</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1683313199700945</v>
+        <v>0.174829931477392</v>
       </c>
       <c r="T83">
-        <v>2.324373861708742</v>
+        <v>2.447650120616657</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.613184280844391</v>
+        <v>2.581316179858483</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07863578766593056</v>
+        <v>0.07869742453754316</v>
       </c>
       <c r="C84">
-        <v>4.704993215616039</v>
+        <v>4.359769173371344</v>
       </c>
       <c r="D84">
-        <v>30.47499321561604</v>
+        <v>30.45976917337135</v>
       </c>
       <c r="E84">
-        <v>9.460000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="F84">
-        <v>27.06</v>
+        <v>27.39</v>
       </c>
       <c r="G84">
         <v>1.29</v>
@@ -8169,28 +8169,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M84">
-        <v>1.945614</v>
+        <v>1.969341</v>
       </c>
       <c r="N84">
-        <v>3.076630897959184</v>
+        <v>3.052903897959184</v>
       </c>
       <c r="O84">
-        <v>0.6153261795918368</v>
+        <v>0.6105807795918369</v>
       </c>
       <c r="P84">
-        <v>2.461304718367347</v>
+        <v>2.442323118367347</v>
       </c>
       <c r="Q84">
-        <v>2.551304718367347</v>
+        <v>2.532323118367347</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.174829931477392</v>
+        <v>0.1820930855149598</v>
       </c>
       <c r="T84">
-        <v>2.447650120616657</v>
+        <v>2.585429468807857</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.581316179858483</v>
+        <v>2.550215984920429</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07869742453754316</v>
+        <v>0.07875906140915578</v>
       </c>
       <c r="C85">
-        <v>4.359769173371344</v>
+        <v>4.014560334131613</v>
       </c>
       <c r="D85">
-        <v>30.45976917337135</v>
+        <v>30.44456033413162</v>
       </c>
       <c r="E85">
-        <v>9.789999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="F85">
-        <v>27.39</v>
+        <v>27.72</v>
       </c>
       <c r="G85">
         <v>1.29</v>
@@ -8251,28 +8251,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M85">
-        <v>1.969341</v>
+        <v>1.993068</v>
       </c>
       <c r="N85">
-        <v>3.052903897959184</v>
+        <v>3.029176897959184</v>
       </c>
       <c r="O85">
-        <v>0.6105807795918369</v>
+        <v>0.6058353795918369</v>
       </c>
       <c r="P85">
-        <v>2.442323118367347</v>
+        <v>2.423341518367347</v>
       </c>
       <c r="Q85">
-        <v>2.532323118367347</v>
+        <v>2.513341518367347</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1820930855149598</v>
+        <v>0.1902641338072236</v>
       </c>
       <c r="T85">
-        <v>2.585429468807857</v>
+        <v>2.740431235522956</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.550215984920429</v>
+        <v>2.519856270814234</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07875906140915578</v>
+        <v>0.08147269828076839</v>
       </c>
       <c r="C86">
-        <v>4.014560334131616</v>
+        <v>3.029702877988662</v>
       </c>
       <c r="D86">
-        <v>30.44456033413162</v>
+        <v>29.78970287798866</v>
       </c>
       <c r="E86">
-        <v>10.12</v>
+        <v>10.45</v>
       </c>
       <c r="F86">
-        <v>27.72</v>
+        <v>28.05</v>
       </c>
       <c r="G86">
         <v>1.29</v>
@@ -8333,45 +8333,45 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M86">
-        <v>1.993068</v>
+        <v>2.12619</v>
       </c>
       <c r="N86">
-        <v>3.029176897959184</v>
+        <v>2.896054897959184</v>
       </c>
       <c r="O86">
-        <v>0.6058353795918369</v>
+        <v>0.5792109795918368</v>
       </c>
       <c r="P86">
-        <v>2.423341518367347</v>
+        <v>2.316843918367347</v>
       </c>
       <c r="Q86">
-        <v>2.513341518367347</v>
+        <v>2.406843918367347</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1902641338072235</v>
+        <v>0.1995246552051225</v>
       </c>
       <c r="T86">
-        <v>2.740431235522955</v>
+        <v>2.916099904466734</v>
       </c>
       <c r="U86">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V86">
         <v>0.2</v>
       </c>
       <c r="W86">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.519856270814234</v>
+        <v>2.362086595252157</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08147269828076839</v>
+        <v>0.08156553515238099</v>
       </c>
       <c r="C87">
-        <v>3.029702877988662</v>
+        <v>2.677797409932946</v>
       </c>
       <c r="D87">
-        <v>29.78970287798866</v>
+        <v>29.76779740993295</v>
       </c>
       <c r="E87">
-        <v>10.45</v>
+        <v>10.78</v>
       </c>
       <c r="F87">
-        <v>28.05</v>
+        <v>28.38</v>
       </c>
       <c r="G87">
         <v>1.29</v>
@@ -8415,28 +8415,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M87">
-        <v>2.12619</v>
+        <v>2.151204</v>
       </c>
       <c r="N87">
-        <v>2.896054897959184</v>
+        <v>2.871040897959184</v>
       </c>
       <c r="O87">
-        <v>0.5792109795918368</v>
+        <v>0.5742081795918369</v>
       </c>
       <c r="P87">
-        <v>2.316843918367347</v>
+        <v>2.296832718367347</v>
       </c>
       <c r="Q87">
-        <v>2.406843918367347</v>
+        <v>2.386832718367347</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1995246552051225</v>
+        <v>0.2101081082312927</v>
       </c>
       <c r="T87">
-        <v>2.916099904466734</v>
+        <v>3.116864097545339</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.362086595252157</v>
+        <v>2.334620472051551</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08156553515238099</v>
+        <v>0.08165837202399359</v>
       </c>
       <c r="C88">
-        <v>2.677797409932946</v>
+        <v>2.325924134003539</v>
       </c>
       <c r="D88">
-        <v>29.76779740993295</v>
+        <v>29.74592413400354</v>
       </c>
       <c r="E88">
-        <v>10.78</v>
+        <v>11.11</v>
       </c>
       <c r="F88">
-        <v>28.38</v>
+        <v>28.71</v>
       </c>
       <c r="G88">
         <v>1.29</v>
@@ -8497,28 +8497,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M88">
-        <v>2.151204</v>
+        <v>2.176218</v>
       </c>
       <c r="N88">
-        <v>2.871040897959184</v>
+        <v>2.846026897959184</v>
       </c>
       <c r="O88">
-        <v>0.5742081795918369</v>
+        <v>0.5692053795918367</v>
       </c>
       <c r="P88">
-        <v>2.296832718367347</v>
+        <v>2.276821518367347</v>
       </c>
       <c r="Q88">
-        <v>2.386832718367347</v>
+        <v>2.366821518367347</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2101081082312927</v>
+        <v>0.2223197847999507</v>
       </c>
       <c r="T88">
-        <v>3.116864097545339</v>
+        <v>3.348515089559113</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.334620472051551</v>
+        <v>2.307785753981992</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08165837202399359</v>
+        <v>0.08175120889560619</v>
       </c>
       <c r="C89">
-        <v>2.325924134003539</v>
+        <v>1.974082979288557</v>
       </c>
       <c r="D89">
-        <v>29.74592413400354</v>
+        <v>29.72408297928856</v>
       </c>
       <c r="E89">
-        <v>11.11</v>
+        <v>11.44</v>
       </c>
       <c r="F89">
-        <v>28.71</v>
+        <v>29.04</v>
       </c>
       <c r="G89">
         <v>1.29</v>
@@ -8579,28 +8579,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M89">
-        <v>2.176218</v>
+        <v>2.201232</v>
       </c>
       <c r="N89">
-        <v>2.846026897959184</v>
+        <v>2.821012897959184</v>
       </c>
       <c r="O89">
-        <v>0.5692053795918367</v>
+        <v>0.5642025795918368</v>
       </c>
       <c r="P89">
-        <v>2.276821518367347</v>
+        <v>2.256810318367347</v>
       </c>
       <c r="Q89">
-        <v>2.366821518367347</v>
+        <v>2.346810318367347</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2223197847999507</v>
+        <v>0.2365667407967183</v>
       </c>
       <c r="T89">
-        <v>3.348515089559113</v>
+        <v>3.618774580241851</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.307785753981992</v>
+        <v>2.281560915868561</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08175120889560619</v>
+        <v>0.08184404576721881</v>
       </c>
       <c r="C90">
-        <v>1.974082979288557</v>
+        <v>1.622273875084229</v>
       </c>
       <c r="D90">
-        <v>29.72408297928856</v>
+        <v>29.70227387508423</v>
       </c>
       <c r="E90">
-        <v>11.44</v>
+        <v>11.77</v>
       </c>
       <c r="F90">
-        <v>29.04</v>
+        <v>29.37</v>
       </c>
       <c r="G90">
         <v>1.29</v>
@@ -8661,28 +8661,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M90">
-        <v>2.201232</v>
+        <v>2.226246</v>
       </c>
       <c r="N90">
-        <v>2.821012897959184</v>
+        <v>2.795998897959184</v>
       </c>
       <c r="O90">
-        <v>0.5642025795918368</v>
+        <v>0.5591997795918368</v>
       </c>
       <c r="P90">
-        <v>2.256810318367347</v>
+        <v>2.236799118367347</v>
       </c>
       <c r="Q90">
-        <v>2.346810318367347</v>
+        <v>2.326799118367347</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2365667407967183</v>
+        <v>0.2534040524292618</v>
       </c>
       <c r="T90">
-        <v>3.618774580241851</v>
+        <v>3.938172160139632</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.281560915868561</v>
+        <v>2.255925399959925</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08184404576721881</v>
+        <v>0.08193688263883142</v>
       </c>
       <c r="C91">
-        <v>1.622273875084229</v>
+        <v>1.270496750894139</v>
       </c>
       <c r="D91">
-        <v>29.70227387508423</v>
+        <v>29.68049675089414</v>
       </c>
       <c r="E91">
-        <v>11.77</v>
+        <v>12.1</v>
       </c>
       <c r="F91">
-        <v>29.37</v>
+        <v>29.7</v>
       </c>
       <c r="G91">
         <v>1.29</v>
@@ -8743,28 +8743,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M91">
-        <v>2.226246</v>
+        <v>2.25126</v>
       </c>
       <c r="N91">
-        <v>2.795998897959184</v>
+        <v>2.770984897959184</v>
       </c>
       <c r="O91">
-        <v>0.5591997795918368</v>
+        <v>0.5541969795918368</v>
       </c>
       <c r="P91">
-        <v>2.236799118367347</v>
+        <v>2.216787918367347</v>
       </c>
       <c r="Q91">
-        <v>2.326799118367347</v>
+        <v>2.306787918367347</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2534040524292618</v>
+        <v>0.2736088263883141</v>
       </c>
       <c r="T91">
-        <v>3.938172160139632</v>
+        <v>4.321449256016969</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.255925399959925</v>
+        <v>2.230859562182593</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08193688263883142</v>
+        <v>0.08202971951044402</v>
       </c>
       <c r="C92">
-        <v>1.270496750894139</v>
+        <v>0.91875153642847</v>
       </c>
       <c r="D92">
-        <v>29.68049675089414</v>
+        <v>29.65875153642847</v>
       </c>
       <c r="E92">
-        <v>12.1</v>
+        <v>12.43</v>
       </c>
       <c r="F92">
-        <v>29.7</v>
+        <v>30.03</v>
       </c>
       <c r="G92">
         <v>1.29</v>
@@ -8825,28 +8825,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M92">
-        <v>2.25126</v>
+        <v>2.276274</v>
       </c>
       <c r="N92">
-        <v>2.770984897959184</v>
+        <v>2.745970897959184</v>
       </c>
       <c r="O92">
-        <v>0.5541969795918368</v>
+        <v>0.5491941795918368</v>
       </c>
       <c r="P92">
-        <v>2.216787918367347</v>
+        <v>2.196776718367347</v>
       </c>
       <c r="Q92">
-        <v>2.306787918367347</v>
+        <v>2.286776718367347</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2736088263883141</v>
+        <v>0.2983035501160446</v>
       </c>
       <c r="T92">
-        <v>4.321449256016969</v>
+        <v>4.789899039867047</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.230859562182593</v>
+        <v>2.206344621938828</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08202971951044402</v>
+        <v>0.08212255638205662</v>
       </c>
       <c r="C93">
-        <v>0.91875153642847</v>
+        <v>0.5670381616032394</v>
       </c>
       <c r="D93">
-        <v>29.65875153642847</v>
+        <v>29.63703816160324</v>
       </c>
       <c r="E93">
-        <v>12.43</v>
+        <v>12.76</v>
       </c>
       <c r="F93">
-        <v>30.03</v>
+        <v>30.36</v>
       </c>
       <c r="G93">
         <v>1.29</v>
@@ -8907,28 +8907,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M93">
-        <v>2.276274</v>
+        <v>2.301288</v>
       </c>
       <c r="N93">
-        <v>2.745970897959184</v>
+        <v>2.720956897959184</v>
       </c>
       <c r="O93">
-        <v>0.5491941795918368</v>
+        <v>0.5441913795918367</v>
       </c>
       <c r="P93">
-        <v>2.196776718367347</v>
+        <v>2.176765518367347</v>
       </c>
       <c r="Q93">
-        <v>2.286776718367347</v>
+        <v>2.266765518367347</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2983035501160446</v>
+        <v>0.3291719547757079</v>
       </c>
       <c r="T93">
-        <v>4.789899039867047</v>
+        <v>5.375461269679645</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.206344621938828</v>
+        <v>2.182362615178623</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08212255638205662</v>
+        <v>0.08221539325366922</v>
       </c>
       <c r="C94">
-        <v>0.5670381616032394</v>
+        <v>0.2153565565395468</v>
       </c>
       <c r="D94">
-        <v>29.63703816160324</v>
+        <v>29.61535655653955</v>
       </c>
       <c r="E94">
-        <v>12.76</v>
+        <v>13.09</v>
       </c>
       <c r="F94">
-        <v>30.36</v>
+        <v>30.69</v>
       </c>
       <c r="G94">
         <v>1.29</v>
@@ -8989,28 +8989,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M94">
-        <v>2.301288</v>
+        <v>2.326302</v>
       </c>
       <c r="N94">
-        <v>2.720956897959184</v>
+        <v>2.695942897959184</v>
       </c>
       <c r="O94">
-        <v>0.5441913795918367</v>
+        <v>0.5391885795918369</v>
       </c>
       <c r="P94">
-        <v>2.176765518367347</v>
+        <v>2.156754318367347</v>
       </c>
       <c r="Q94">
-        <v>2.266765518367347</v>
+        <v>2.246754318367347</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3291719547757079</v>
+        <v>0.3688599036238463</v>
       </c>
       <c r="T94">
-        <v>5.375461269679645</v>
+        <v>6.128326993724414</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.182362615178623</v>
+        <v>2.158896350499283</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08221539325366922</v>
+        <v>0.08230823012528184</v>
       </c>
       <c r="C95">
-        <v>0.2153565565395468</v>
+        <v>-0.1362933484371744</v>
       </c>
       <c r="D95">
-        <v>29.61535655653955</v>
+        <v>29.59370665156283</v>
       </c>
       <c r="E95">
-        <v>13.09</v>
+        <v>13.42</v>
       </c>
       <c r="F95">
-        <v>30.69</v>
+        <v>31.02</v>
       </c>
       <c r="G95">
         <v>1.29</v>
@@ -9071,28 +9071,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M95">
-        <v>2.326302</v>
+        <v>2.351316000000001</v>
       </c>
       <c r="N95">
-        <v>2.695942897959184</v>
+        <v>2.670928897959183</v>
       </c>
       <c r="O95">
-        <v>0.5391885795918369</v>
+        <v>0.5341857795918367</v>
       </c>
       <c r="P95">
-        <v>2.156754318367347</v>
+        <v>2.136743118367347</v>
       </c>
       <c r="Q95">
-        <v>2.246754318367347</v>
+        <v>2.226743118367347</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3688599036238463</v>
+        <v>0.4217771687546975</v>
       </c>
       <c r="T95">
-        <v>6.128326993724414</v>
+        <v>7.13214795911744</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.158896350499283</v>
+        <v>2.135929368047163</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08230823012528184</v>
+        <v>0.08240106699689445</v>
       </c>
       <c r="C96">
-        <v>-0.1362933484371744</v>
+        <v>-0.4879116227978813</v>
       </c>
       <c r="D96">
-        <v>29.59370665156283</v>
+        <v>29.57208837720212</v>
       </c>
       <c r="E96">
-        <v>13.42</v>
+        <v>13.75</v>
       </c>
       <c r="F96">
-        <v>31.02</v>
+        <v>31.35</v>
       </c>
       <c r="G96">
         <v>1.29</v>
@@ -9153,28 +9153,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M96">
-        <v>2.351316000000001</v>
+        <v>2.37633</v>
       </c>
       <c r="N96">
-        <v>2.670928897959183</v>
+        <v>2.645914897959184</v>
       </c>
       <c r="O96">
-        <v>0.5341857795918367</v>
+        <v>0.5291829795918368</v>
       </c>
       <c r="P96">
-        <v>2.136743118367347</v>
+        <v>2.116731918367347</v>
       </c>
       <c r="Q96">
-        <v>2.226743118367347</v>
+        <v>2.206731918367347</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4217771687546975</v>
+        <v>0.4958613399378894</v>
       </c>
       <c r="T96">
-        <v>7.13214795911744</v>
+        <v>8.53749731066768</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.135929368047163</v>
+        <v>2.113445901015088</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08240106699689445</v>
+        <v>0.08249390386850705</v>
       </c>
       <c r="C97">
-        <v>-0.4879116227978813</v>
+        <v>-0.8394983358107062</v>
       </c>
       <c r="D97">
-        <v>29.57208837720212</v>
+        <v>29.5505016641893</v>
       </c>
       <c r="E97">
-        <v>13.75</v>
+        <v>14.08</v>
       </c>
       <c r="F97">
-        <v>31.35</v>
+        <v>31.68</v>
       </c>
       <c r="G97">
         <v>1.29</v>
@@ -9235,28 +9235,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M97">
-        <v>2.37633</v>
+        <v>2.401344</v>
       </c>
       <c r="N97">
-        <v>2.645914897959184</v>
+        <v>2.620900897959184</v>
       </c>
       <c r="O97">
-        <v>0.5291829795918368</v>
+        <v>0.5241801795918367</v>
       </c>
       <c r="P97">
-        <v>2.116731918367347</v>
+        <v>2.096720718367347</v>
       </c>
       <c r="Q97">
-        <v>2.206731918367347</v>
+        <v>2.186720718367347</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4958613399378894</v>
+        <v>0.6069875967126771</v>
       </c>
       <c r="T97">
-        <v>8.53749731066768</v>
+        <v>10.64552133799304</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.113445901015088</v>
+        <v>2.09143083954618</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08249390386850705</v>
+        <v>0.08258674074011965</v>
       </c>
       <c r="C98">
-        <v>-0.8394983358107027</v>
+        <v>-1.191053556541657</v>
       </c>
       <c r="D98">
-        <v>29.5505016641893</v>
+        <v>29.52894644345834</v>
       </c>
       <c r="E98">
-        <v>14.08</v>
+        <v>14.41</v>
       </c>
       <c r="F98">
-        <v>31.68</v>
+        <v>32.01</v>
       </c>
       <c r="G98">
         <v>1.29</v>
@@ -9317,28 +9317,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M98">
-        <v>2.401344</v>
+        <v>2.426358</v>
       </c>
       <c r="N98">
-        <v>2.620900897959184</v>
+        <v>2.595886897959184</v>
       </c>
       <c r="O98">
-        <v>0.5241801795918367</v>
+        <v>0.5191773795918369</v>
       </c>
       <c r="P98">
-        <v>2.096720718367347</v>
+        <v>2.076709518367347</v>
       </c>
       <c r="Q98">
-        <v>2.186720718367347</v>
+        <v>2.166709518367347</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6069875967126755</v>
+        <v>0.7921980246706544</v>
       </c>
       <c r="T98">
-        <v>10.64552133799301</v>
+        <v>14.15889471686859</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.09143083954618</v>
+        <v>2.069869696870447</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08258674074011965</v>
+        <v>0.08267957761173227</v>
       </c>
       <c r="C99">
-        <v>-1.191053556541657</v>
+        <v>-1.542577353855396</v>
       </c>
       <c r="D99">
-        <v>29.52894644345834</v>
+        <v>29.5074226461446</v>
       </c>
       <c r="E99">
-        <v>14.41</v>
+        <v>14.73999999999999</v>
       </c>
       <c r="F99">
-        <v>32.01</v>
+        <v>32.34</v>
       </c>
       <c r="G99">
         <v>1.29</v>
@@ -9399,28 +9399,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M99">
-        <v>2.426358</v>
+        <v>2.451372</v>
       </c>
       <c r="N99">
-        <v>2.595886897959184</v>
+        <v>2.570872897959184</v>
       </c>
       <c r="O99">
-        <v>0.5191773795918369</v>
+        <v>0.5141745795918368</v>
       </c>
       <c r="P99">
-        <v>2.076709518367347</v>
+        <v>2.056698318367347</v>
       </c>
       <c r="Q99">
-        <v>2.166709518367347</v>
+        <v>2.146698318367347</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7921980246706544</v>
+        <v>1.162618880586612</v>
       </c>
       <c r="T99">
-        <v>14.15889471686859</v>
+        <v>21.18564147461975</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.069869696870447</v>
+        <v>2.048748577514626</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08267957761173227</v>
+        <v>0.08277241448334487</v>
       </c>
       <c r="C100">
-        <v>-1.542577353855396</v>
+        <v>-1.894069796415934</v>
       </c>
       <c r="D100">
-        <v>29.5074226461446</v>
+        <v>29.48593020358407</v>
       </c>
       <c r="E100">
-        <v>14.73999999999999</v>
+        <v>15.07</v>
       </c>
       <c r="F100">
-        <v>32.34</v>
+        <v>32.67</v>
       </c>
       <c r="G100">
         <v>1.29</v>
@@ -9481,28 +9481,28 @@
         <v>5.022244897959184</v>
       </c>
       <c r="M100">
-        <v>2.451372</v>
+        <v>2.476386</v>
       </c>
       <c r="N100">
-        <v>2.570872897959184</v>
+        <v>2.545858897959184</v>
       </c>
       <c r="O100">
-        <v>0.5141745795918368</v>
+        <v>0.5091717795918368</v>
       </c>
       <c r="P100">
-        <v>2.056698318367347</v>
+        <v>2.036687118367347</v>
       </c>
       <c r="Q100">
-        <v>2.146698318367347</v>
+        <v>2.126687118367347</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.162618880586612</v>
+        <v>2.273881448334484</v>
       </c>
       <c r="T100">
-        <v>21.18564147461975</v>
+        <v>42.26588174787323</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.048748577514626</v>
+        <v>2.028054147438721</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08277241448334487</v>
-      </c>
-      <c r="C101">
-        <v>-1.894069796415934</v>
-      </c>
-      <c r="D101">
-        <v>29.48593020358407</v>
-      </c>
-      <c r="E101">
-        <v>15.07</v>
-      </c>
-      <c r="F101">
-        <v>32.67</v>
-      </c>
-      <c r="G101">
-        <v>1.29</v>
-      </c>
-      <c r="H101">
-        <v>15.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.112244897959184</v>
-      </c>
-      <c r="K101">
-        <v>0.08999999999999986</v>
-      </c>
-      <c r="L101">
-        <v>5.022244897959184</v>
-      </c>
-      <c r="M101">
-        <v>2.476386</v>
-      </c>
-      <c r="N101">
-        <v>2.545858897959184</v>
-      </c>
-      <c r="O101">
-        <v>0.5091717795918368</v>
-      </c>
-      <c r="P101">
-        <v>2.036687118367347</v>
-      </c>
-      <c r="Q101">
-        <v>2.126687118367347</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.273881448334484</v>
-      </c>
-      <c r="T101">
-        <v>42.26588174787323</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.06064000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.028054147438721</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
